--- a/Data_processed/coral_lumn.xlsx
+++ b/Data_processed/coral_lumn.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GDrive\Academicos\Articulos\Pendientes\Varadero growth rates\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GDrive\Academicos\Articulos\Pendientes\Varadero growth rates\Data_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9ED1FC6-438F-4436-8B4F-7FDCDCA8DB7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE58C54B-DF38-4718-909C-96F2533DEA02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00D95527-D75E-4AD9-900B-59FC494863D4}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00D95527-D75E-4AD9-900B-59FC494863D4}"/>
   </bookViews>
   <sheets>
     <sheet name="indexed" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="31">
   <si>
     <t>Core</t>
   </si>
@@ -75,6 +75,66 @@
   <si>
     <t>stda</t>
   </si>
+  <si>
+    <t>g/b</t>
+  </si>
+  <si>
+    <t>XLSTAT 2016.02.28451  - Correlation tests - Start time: 11/22/2025 at 10:54:40 AM</t>
+  </si>
+  <si>
+    <t>Observations/variables table: Workbook = coral_lumn.xlsx / Sheet = waterflow / Range = waterflow!$C$1:$D$35 / 34 rows and 2 columns</t>
+  </si>
+  <si>
+    <t>Type of correlation: Pearson</t>
+  </si>
+  <si>
+    <t>Summary statistics:</t>
+  </si>
+  <si>
+    <t>Variable</t>
+  </si>
+  <si>
+    <t>Observations</t>
+  </si>
+  <si>
+    <t>Obs. with missing data</t>
+  </si>
+  <si>
+    <t>Obs. without missing data</t>
+  </si>
+  <si>
+    <t>Minimum</t>
+  </si>
+  <si>
+    <t>Maximum</t>
+  </si>
+  <si>
+    <t>Mean</t>
+  </si>
+  <si>
+    <t>Std. deviation</t>
+  </si>
+  <si>
+    <t>Correlation matrix (Pearson):</t>
+  </si>
+  <si>
+    <t>Variables</t>
+  </si>
+  <si>
+    <t>Values in bold are different from 0 with a significance level alpha=0.05</t>
+  </si>
+  <si>
+    <t>p-values:</t>
+  </si>
+  <si>
+    <t>Coefficients of determination (R²):</t>
+  </si>
+  <si>
+    <t>centered</t>
+  </si>
+  <si>
+    <t>center</t>
+  </si>
 </sst>
 </file>
 
@@ -84,7 +144,7 @@
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -100,6 +160,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -109,7 +177,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -117,16 +185,66 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -299,9 +417,6 @@
                 <c:pt idx="33">
                   <c:v>1982</c:v>
                 </c:pt>
-                <c:pt idx="34">
-                  <c:v>1981</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -412,9 +527,6 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>239.70833333333334</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>256.24583333333334</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -994,7 +1106,7 @@
                 <c:order val="3"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>columns!$G$2</c15:sqref>
@@ -1023,7 +1135,7 @@
                 </c:marker>
                 <c:xVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>columns!$H$2:$H$36</c15:sqref>
@@ -1143,7 +1255,7 @@
                 </c:xVal>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>columns!$I$2:$I$36</c15:sqref>
@@ -1262,7 +1374,7 @@
                   </c:numRef>
                 </c:yVal>
                 <c:smooth val="0"/>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000003-BF29-470C-8DCC-3FA3FEF92186}"/>
                   </c:ext>
@@ -1275,7 +1387,7 @@
                 <c:order val="4"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>columns!$J$2</c15:sqref>
@@ -1304,7 +1416,7 @@
                 </c:marker>
                 <c:xVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>columns!$K$2:$K$36</c15:sqref>
@@ -1424,7 +1536,7 @@
                 </c:xVal>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>columns!$L$2:$L$36</c15:sqref>
@@ -1543,7 +1655,7 @@
                   </c:numRef>
                 </c:yVal>
                 <c:smooth val="0"/>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000004-BF29-470C-8DCC-3FA3FEF92186}"/>
                   </c:ext>
@@ -1739,6 +1851,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="1571430321"/>
+        <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:spPr>
@@ -1975,9 +2088,6 @@
                 <c:pt idx="33">
                   <c:v>1982</c:v>
                 </c:pt>
-                <c:pt idx="34">
-                  <c:v>1981</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -1985,112 +2095,109 @@
             <c:numRef>
               <c:f>waterflow!$C$2:$C$36</c:f>
               <c:numCache>
-                <c:formatCode>0.0</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="35"/>
                 <c:pt idx="0">
-                  <c:v>-1.0404239729056239</c:v>
+                  <c:v>-105.44338235294111</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-0.36362350582824182</c:v>
+                  <c:v>-38.876715686274451</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-0.69160230002660761</c:v>
+                  <c:v>-71.135049019607777</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-5.6911226056068485E-2</c:v>
+                  <c:v>-8.7100490196078226</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.5639191363863867</c:v>
+                  <c:v>150.70661764705898</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.0499642498952226</c:v>
+                  <c:v>100.15661764705874</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.58142311532613034</c:v>
+                  <c:v>54.073284313725594</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.0174635655633044</c:v>
+                  <c:v>195.31495098039221</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.5269780993751516</c:v>
+                  <c:v>147.07328431372554</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.2234854512690942</c:v>
+                  <c:v>117.22328431372551</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.40391973794416697</c:v>
+                  <c:v>36.614950980392166</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>8.8565288962943814E-2</c:v>
+                  <c:v>5.5982843137255713</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>4.9929708969542803E-2</c:v>
+                  <c:v>1.79828431372556</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-5.2276650999835781E-3</c:v>
+                  <c:v>-3.6267156862744514</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-0.78514107264221022</c:v>
+                  <c:v>-80.335049019607823</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.5220639247268686</c:v>
+                  <c:v>146.58995098039225</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.7870057199886329</c:v>
+                  <c:v>172.64828431372558</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-3.7932344655801302E-2</c:v>
+                  <c:v>-6.8433823529411484</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-1.4992214853272599</c:v>
+                  <c:v>-150.56838235294114</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.4611105635922933</c:v>
+                  <c:v>42.239950980392166</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.29945116309359038</c:v>
+                  <c:v>26.339950980392246</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.23310980534176295</c:v>
+                  <c:v>19.814950980392155</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>-0.38539838314908381</c:v>
+                  <c:v>-41.018382352941103</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-1.1512470839393263</c:v>
+                  <c:v>-116.34338235294109</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-1.2126742670428698</c:v>
+                  <c:v>-122.38504901960781</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>-0.4673295363368441</c:v>
+                  <c:v>-49.07671568627444</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>7.3568583570768231E-2</c:v>
+                  <c:v>4.1232843137255486</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.7636712130581591</c:v>
+                  <c:v>71.998284313725549</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>-0.5035927561552116</c:v>
+                  <c:v>-52.643382352941103</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>-0.45546773546167696</c:v>
+                  <c:v>-47.910049019607754</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>-0.59009917539482182</c:v>
+                  <c:v>-61.151715686274429</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>5.1937742403414307E-3</c:v>
+                  <c:v>-2.6017156862744741</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>-2.0848555399640731</c:v>
+                  <c:v>-208.16838235294111</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>-1.244108039362062</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>-1.0759670119565707</c:v>
+                  <c:v>-125.47671568627445</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2259,111 +2366,111 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>columns!$O$2:$O$35</c:f>
+              <c:f>columns!$P$2:$P$35</c:f>
               <c:numCache>
-                <c:formatCode>0.0</c:formatCode>
+                <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="34"/>
                 <c:pt idx="0">
-                  <c:v>-1.5771752669169647</c:v>
+                  <c:v>-3.5011831280982286E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-2.1765114433357593</c:v>
+                  <c:v>-4.5220164614313885E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-2.0982307998851368</c:v>
+                  <c:v>-4.3886831280980698E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-1.1894414548254602</c:v>
+                  <c:v>-2.8407664614313988E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-0.46045296269154867</c:v>
+                  <c:v>-1.5990997947648911E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-0.53873360614211929</c:v>
+                  <c:v>-1.7324331280981209E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-1.0218719524389888</c:v>
+                  <c:v>-2.5553497947647941E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-0.36749469859395367</c:v>
+                  <c:v>-1.4407664614316085E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-8.4950501139376744E-2</c:v>
+                  <c:v>-9.5951646143168645E-3</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.7577923821043408E-2</c:v>
+                  <c:v>-7.6784979476478554E-3</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-0.34792453773131099</c:v>
+                  <c:v>-1.407433128098301E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-0.14733038888914882</c:v>
+                  <c:v>-1.0657664614317719E-2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-0.20114833126145848</c:v>
+                  <c:v>-1.1574331280984396E-2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-0.37727977902528154</c:v>
+                  <c:v>-1.4574331280982733E-2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-0.72465013433756353</c:v>
+                  <c:v>-2.0490997947651191E-2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-0.22928043750147228</c:v>
+                  <c:v>-1.2053497947650094E-2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.073358394919036</c:v>
+                  <c:v>1.0134002052347268E-2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-0.57420452270569089</c:v>
+                  <c:v>-1.7928497947647948E-2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-1.4108288995843261</c:v>
+                  <c:v>-3.2178497947648155E-2</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.0978210959974013</c:v>
+                  <c:v>1.0550668719014666E-2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.9791769957676798</c:v>
+                  <c:v>8.5298353856837483E-3</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.70397160863651731</c:v>
+                  <c:v>3.8423353856831266E-3</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.56086480732828725</c:v>
+                  <c:v>1.4048353856823681E-3</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>2.8801058874895837E-2</c:v>
+                  <c:v>-7.6576646143156069E-3</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.87765678629259636</c:v>
+                  <c:v>6.8006687190163007E-3</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.7901155365141299</c:v>
+                  <c:v>2.2342335385684864E-2</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1.7277356487643969</c:v>
+                  <c:v>2.1279835385684676E-2</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1.3933907387390998</c:v>
+                  <c:v>1.5585027656514594E-2</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.45606239810942789</c:v>
+                  <c:v>-3.8023611431459159E-4</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.69018592008731783</c:v>
+                  <c:v>3.6075274273505986E-3</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.50956717020556808</c:v>
+                  <c:v>5.3109640651705092E-4</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.81254327242419555</c:v>
+                  <c:v>5.6916075940147692E-3</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.18321498541283629</c:v>
+                  <c:v>-5.02757336431503E-3</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.61546537511135313</c:v>
+                  <c:v>2.3348323023530959E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2668,7 +2775,7 @@
                 <c:order val="2"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>columns!$D$2</c15:sqref>
@@ -2697,7 +2804,7 @@
                 </c:marker>
                 <c:xVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>columns!$E$2:$E$36</c15:sqref>
@@ -2817,7 +2924,7 @@
                 </c:xVal>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>columns!$F$2:$F$36</c15:sqref>
@@ -2936,7 +3043,7 @@
                   </c:numRef>
                 </c:yVal>
                 <c:smooth val="0"/>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000002-98CB-4519-A278-1D0CF063AAF3}"/>
                   </c:ext>
@@ -2949,7 +3056,7 @@
                 <c:order val="3"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>columns!$G$2</c15:sqref>
@@ -2978,7 +3085,7 @@
                 </c:marker>
                 <c:xVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>columns!$H$2:$H$36</c15:sqref>
@@ -3098,7 +3205,7 @@
                 </c:xVal>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>columns!$I$2:$I$36</c15:sqref>
@@ -3217,7 +3324,7 @@
                   </c:numRef>
                 </c:yVal>
                 <c:smooth val="0"/>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000003-98CB-4519-A278-1D0CF063AAF3}"/>
                   </c:ext>
@@ -3230,7 +3337,7 @@
                 <c:order val="4"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>columns!$J$2</c15:sqref>
@@ -3259,7 +3366,7 @@
                 </c:marker>
                 <c:xVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>columns!$K$2:$K$36</c15:sqref>
@@ -3379,7 +3486,7 @@
                 </c:xVal>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>columns!$L$2:$L$36</c15:sqref>
@@ -3498,7 +3605,7 @@
                   </c:numRef>
                 </c:yVal>
                 <c:smooth val="0"/>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000004-98CB-4519-A278-1D0CF063AAF3}"/>
                   </c:ext>
@@ -3837,112 +3944,109 @@
             <c:numRef>
               <c:f>waterflow!$C$2:$C$36</c:f>
               <c:numCache>
-                <c:formatCode>0.0</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="35"/>
                 <c:pt idx="0">
-                  <c:v>-1.0404239729056239</c:v>
+                  <c:v>-105.44338235294111</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-0.36362350582824182</c:v>
+                  <c:v>-38.876715686274451</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-0.69160230002660761</c:v>
+                  <c:v>-71.135049019607777</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-5.6911226056068485E-2</c:v>
+                  <c:v>-8.7100490196078226</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.5639191363863867</c:v>
+                  <c:v>150.70661764705898</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.0499642498952226</c:v>
+                  <c:v>100.15661764705874</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.58142311532613034</c:v>
+                  <c:v>54.073284313725594</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.0174635655633044</c:v>
+                  <c:v>195.31495098039221</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.5269780993751516</c:v>
+                  <c:v>147.07328431372554</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.2234854512690942</c:v>
+                  <c:v>117.22328431372551</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.40391973794416697</c:v>
+                  <c:v>36.614950980392166</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>8.8565288962943814E-2</c:v>
+                  <c:v>5.5982843137255713</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>4.9929708969542803E-2</c:v>
+                  <c:v>1.79828431372556</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-5.2276650999835781E-3</c:v>
+                  <c:v>-3.6267156862744514</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-0.78514107264221022</c:v>
+                  <c:v>-80.335049019607823</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.5220639247268686</c:v>
+                  <c:v>146.58995098039225</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.7870057199886329</c:v>
+                  <c:v>172.64828431372558</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-3.7932344655801302E-2</c:v>
+                  <c:v>-6.8433823529411484</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-1.4992214853272599</c:v>
+                  <c:v>-150.56838235294114</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.4611105635922933</c:v>
+                  <c:v>42.239950980392166</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.29945116309359038</c:v>
+                  <c:v>26.339950980392246</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.23310980534176295</c:v>
+                  <c:v>19.814950980392155</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>-0.38539838314908381</c:v>
+                  <c:v>-41.018382352941103</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-1.1512470839393263</c:v>
+                  <c:v>-116.34338235294109</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-1.2126742670428698</c:v>
+                  <c:v>-122.38504901960781</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>-0.4673295363368441</c:v>
+                  <c:v>-49.07671568627444</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>7.3568583570768231E-2</c:v>
+                  <c:v>4.1232843137255486</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.7636712130581591</c:v>
+                  <c:v>71.998284313725549</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>-0.5035927561552116</c:v>
+                  <c:v>-52.643382352941103</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>-0.45546773546167696</c:v>
+                  <c:v>-47.910049019607754</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>-0.59009917539482182</c:v>
+                  <c:v>-61.151715686274429</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>5.1937742403414307E-3</c:v>
+                  <c:v>-2.6017156862744741</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>-2.0848555399640731</c:v>
+                  <c:v>-208.16838235294111</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>-1.244108039362062</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>-1.0759670119565707</c:v>
+                  <c:v>-125.47671568627445</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3954,106 +4058,106 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="34"/>
                 <c:pt idx="0">
-                  <c:v>-1.5771752669169647</c:v>
+                  <c:v>-2.0659110372486018</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-2.1765114433357593</c:v>
+                  <c:v>-2.6682648054931648</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-2.0982307998851368</c:v>
+                  <c:v>-2.5895900275999928</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-1.1894414548254602</c:v>
+                  <c:v>-1.676225027996344</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-0.46045296269154867</c:v>
+                  <c:v>-0.94356615886619133</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-0.53873360614211929</c:v>
+                  <c:v>-1.022240936759311</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-1.0218719524389888</c:v>
+                  <c:v>-1.5078118315687905</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-0.36749469859395367</c:v>
+                  <c:v>-0.85013986011806908</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-8.4950501139376744E-2</c:v>
+                  <c:v>-0.56617308365991559</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.7577923821043408E-2</c:v>
+                  <c:v>-0.45307809043832992</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-0.34792453773131099</c:v>
+                  <c:v>-0.83047116564478918</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-0.14733038888914882</c:v>
+                  <c:v>-0.62886704729359444</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-0.20114833126145848</c:v>
+                  <c:v>-0.68295595709515688</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-0.37727977902528154</c:v>
+                  <c:v>-0.85997420735471564</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-0.72465013433756353</c:v>
+                  <c:v>-1.2090935342558111</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-0.22928043750147228</c:v>
+                  <c:v>-0.7112297054004616</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.073358394919036</c:v>
+                  <c:v>0.59796777047809502</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-0.57420452270569089</c:v>
+                  <c:v>-1.0578904454921629</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-1.4108288995843261</c:v>
+                  <c:v>-1.8987271342255452</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.0978210959974013</c:v>
+                  <c:v>0.62255363856975721</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.9791769957676798</c:v>
+                  <c:v>0.50331217832554753</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.70397160863651731</c:v>
+                  <c:v>0.22672116229479697</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.56086480732828725</c:v>
+                  <c:v>8.2893833958780999E-2</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>2.8801058874895837E-2</c:v>
+                  <c:v>-0.45184879703381298</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.87765678629259636</c:v>
+                  <c:v>0.40128082574528251</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.7901155365141299</c:v>
+                  <c:v>1.3183337055627835</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1.7277356487643969</c:v>
+                  <c:v>1.2556397419291438</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1.3933907387390998</c:v>
+                  <c:v>0.91961144200152467</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.45606239810942789</c:v>
+                  <c:v>-2.2436243880499956E-2</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.69018592008731783</c:v>
+                  <c:v>0.2128660643177748</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.50956717020556808</c:v>
+                  <c:v>3.133791886694659E-2</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.81254327242419555</c:v>
+                  <c:v>0.33583947248568996</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.18321498541283629</c:v>
+                  <c:v>-0.29665741333436768</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.61546537511135313</c:v>
+                  <c:v>0.1377693096040904</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4097,7 +4201,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -4406,122 +4510,116 @@
                 <c:pt idx="33">
                   <c:v>1982</c:v>
                 </c:pt>
-                <c:pt idx="34">
-                  <c:v>1981</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>waterflow!$C$2:$C$36</c:f>
+              <c:f>waterflow!$D$2:$D$36</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="35"/>
                 <c:pt idx="0">
-                  <c:v>-1.0404239729056239</c:v>
+                  <c:v>-1.0751984741460796</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-0.36362350582824182</c:v>
+                  <c:v>-0.39642303246475213</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-0.69160230002660761</c:v>
+                  <c:v>-0.72535890311427864</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-5.6911226056068485E-2</c:v>
+                  <c:v>-8.8815734156489426E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.5639191363863867</c:v>
+                  <c:v>1.5367443809366259</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.0499642498952226</c:v>
+                  <c:v>1.0212897202907882</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.58142311532613034</c:v>
+                  <c:v>0.5513813336486092</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.0174635655633044</c:v>
+                  <c:v>1.9916123002305841</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.5269780993751516</c:v>
+                  <c:v>1.4996955461127566</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.2234854512690942</c:v>
+                  <c:v>1.195317274692812</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.40391973794416697</c:v>
+                  <c:v>0.37335998283208582</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>8.8565288962943814E-2</c:v>
+                  <c:v>5.7085296560441492E-2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>4.9929708969542803E-2</c:v>
+                  <c:v>1.833697390061597E-2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-5.2276650999835781E-3</c:v>
+                  <c:v>-3.6981355159792777E-2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-0.78514107264221022</c:v>
+                  <c:v>-0.81917063165911952</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.5220639247268686</c:v>
+                  <c:v>1.4947670313884811</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.7870057199886329</c:v>
+                  <c:v>1.7604819545403978</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-3.7932344655801302E-2</c:v>
+                  <c:v>-6.97814703937681E-2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-1.4992214853272599</c:v>
+                  <c:v>-1.5353348057315064</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.4611105635922933</c:v>
+                  <c:v>0.43071769729564319</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.29945116309359038</c:v>
+                  <c:v>0.26858655774532192</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.23310980534176295</c:v>
+                  <c:v>0.20205160896759444</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>-0.38539838314908381</c:v>
+                  <c:v>-0.41826145115680269</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-1.1512470839393263</c:v>
+                  <c:v>-1.1863449786176838</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-1.2126742670428698</c:v>
+                  <c:v>-1.2479514126711346</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>-0.4673295363368441</c:v>
+                  <c:v>-0.500431688025336</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>7.3568583570768231E-2</c:v>
+                  <c:v>4.2044829212219553E-2</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.7636712130581591</c:v>
+                  <c:v>0.73416125040581148</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>-0.5035927561552116</c:v>
+                  <c:v>-0.53680072771482124</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>-0.45546773546167696</c:v>
+                  <c:v>-0.48853527317363499</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>-0.59009917539482182</c:v>
+                  <c:v>-0.62355958174043891</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>5.1937742403414307E-3</c:v>
+                  <c:v>-2.6529504968655897E-2</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>-2.0848555399640731</c:v>
+                  <c:v>-2.1226778018383334</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>-1.244108039362062</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>-1.0759670119565707</c:v>
+                  <c:v>-1.2794769120281415</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5532,7 +5630,7 @@
                   </c:numRef>
                 </c:yVal>
                 <c:smooth val="0"/>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000004-8444-4561-BB73-D22980E5C873}"/>
                   </c:ext>
@@ -5813,7 +5911,7 @@
                   </c:numRef>
                 </c:yVal>
                 <c:smooth val="0"/>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000005-8444-4561-BB73-D22980E5C873}"/>
                   </c:ext>
@@ -5853,7 +5951,7 @@
                 </c:marker>
                 <c:xVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>columns!$K$2:$K$35</c15:sqref>
@@ -5970,7 +6068,7 @@
                 </c:xVal>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>columns!$O$2:$O$35</c15:sqref>
@@ -5981,112 +6079,112 @@
                       <c:formatCode>0.0</c:formatCode>
                       <c:ptCount val="34"/>
                       <c:pt idx="0">
-                        <c:v>-1.5771752669169647</c:v>
+                        <c:v>-2.0659110372486018</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>-2.1765114433357593</c:v>
+                        <c:v>-2.6682648054931648</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>-2.0982307998851368</c:v>
+                        <c:v>-2.5895900275999928</c:v>
                       </c:pt>
                       <c:pt idx="3">
-                        <c:v>-1.1894414548254602</c:v>
+                        <c:v>-1.676225027996344</c:v>
                       </c:pt>
                       <c:pt idx="4">
-                        <c:v>-0.46045296269154867</c:v>
+                        <c:v>-0.94356615886619133</c:v>
                       </c:pt>
                       <c:pt idx="5">
-                        <c:v>-0.53873360614211929</c:v>
+                        <c:v>-1.022240936759311</c:v>
                       </c:pt>
                       <c:pt idx="6">
-                        <c:v>-1.0218719524389888</c:v>
+                        <c:v>-1.5078118315687905</c:v>
                       </c:pt>
                       <c:pt idx="7">
-                        <c:v>-0.36749469859395367</c:v>
+                        <c:v>-0.85013986011806908</c:v>
                       </c:pt>
                       <c:pt idx="8">
-                        <c:v>-8.4950501139376744E-2</c:v>
+                        <c:v>-0.56617308365991559</c:v>
                       </c:pt>
                       <c:pt idx="9">
-                        <c:v>2.7577923821043408E-2</c:v>
+                        <c:v>-0.45307809043832992</c:v>
                       </c:pt>
                       <c:pt idx="10">
-                        <c:v>-0.34792453773131099</c:v>
+                        <c:v>-0.83047116564478918</c:v>
                       </c:pt>
                       <c:pt idx="11">
-                        <c:v>-0.14733038888914882</c:v>
+                        <c:v>-0.62886704729359444</c:v>
                       </c:pt>
                       <c:pt idx="12">
-                        <c:v>-0.20114833126145848</c:v>
+                        <c:v>-0.68295595709515688</c:v>
                       </c:pt>
                       <c:pt idx="13">
-                        <c:v>-0.37727977902528154</c:v>
+                        <c:v>-0.85997420735471564</c:v>
                       </c:pt>
                       <c:pt idx="14">
-                        <c:v>-0.72465013433756353</c:v>
+                        <c:v>-1.2090935342558111</c:v>
                       </c:pt>
                       <c:pt idx="15">
-                        <c:v>-0.22928043750147228</c:v>
+                        <c:v>-0.7112297054004616</c:v>
                       </c:pt>
                       <c:pt idx="16">
-                        <c:v>1.073358394919036</c:v>
+                        <c:v>0.59796777047809502</c:v>
                       </c:pt>
                       <c:pt idx="17">
-                        <c:v>-0.57420452270569089</c:v>
+                        <c:v>-1.0578904454921629</c:v>
                       </c:pt>
                       <c:pt idx="18">
-                        <c:v>-1.4108288995843261</c:v>
+                        <c:v>-1.8987271342255452</c:v>
                       </c:pt>
                       <c:pt idx="19">
-                        <c:v>1.0978210959974013</c:v>
+                        <c:v>0.62255363856975721</c:v>
                       </c:pt>
                       <c:pt idx="20">
-                        <c:v>0.9791769957676798</c:v>
+                        <c:v>0.50331217832554753</c:v>
                       </c:pt>
                       <c:pt idx="21">
-                        <c:v>0.70397160863651731</c:v>
+                        <c:v>0.22672116229479697</c:v>
                       </c:pt>
                       <c:pt idx="22">
-                        <c:v>0.56086480732828725</c:v>
+                        <c:v>8.2893833958780999E-2</c:v>
                       </c:pt>
                       <c:pt idx="23">
-                        <c:v>2.8801058874895837E-2</c:v>
+                        <c:v>-0.45184879703381298</c:v>
                       </c:pt>
                       <c:pt idx="24">
-                        <c:v>0.87765678629259636</c:v>
+                        <c:v>0.40128082574528251</c:v>
                       </c:pt>
                       <c:pt idx="25">
-                        <c:v>1.7901155365141299</c:v>
+                        <c:v>1.3183337055627835</c:v>
                       </c:pt>
                       <c:pt idx="26">
-                        <c:v>1.7277356487643969</c:v>
+                        <c:v>1.2556397419291438</c:v>
                       </c:pt>
                       <c:pt idx="27">
-                        <c:v>1.3933907387390998</c:v>
+                        <c:v>0.91961144200152467</c:v>
                       </c:pt>
                       <c:pt idx="28">
-                        <c:v>0.45606239810942789</c:v>
+                        <c:v>-2.2436243880499956E-2</c:v>
                       </c:pt>
                       <c:pt idx="29">
-                        <c:v>0.69018592008731783</c:v>
+                        <c:v>0.2128660643177748</c:v>
                       </c:pt>
                       <c:pt idx="30">
-                        <c:v>0.50956717020556808</c:v>
+                        <c:v>3.133791886694659E-2</c:v>
                       </c:pt>
                       <c:pt idx="31">
-                        <c:v>0.81254327242419555</c:v>
+                        <c:v>0.33583947248568996</c:v>
                       </c:pt>
                       <c:pt idx="32">
-                        <c:v>0.18321498541283629</c:v>
+                        <c:v>-0.29665741333436768</c:v>
                       </c:pt>
                       <c:pt idx="33">
-                        <c:v>0.61546537511135313</c:v>
+                        <c:v>0.1377693096040904</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
                 </c:yVal>
                 <c:smooth val="0"/>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000001-8444-4561-BB73-D22980E5C873}"/>
                   </c:ext>
@@ -8593,16 +8691,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>472440</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>148590</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>289560</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>148590</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -8629,16 +8727,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>480060</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>297180</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -8667,16 +8765,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>441960</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>249555</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>259080</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>68580</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>120015</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -8705,16 +8803,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>495300</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>312420</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
       <xdr:row>47</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -12234,7 +12332,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73690CDD-5C49-454D-B115-5B41D8C27B42}">
-  <dimension ref="A1:P66"/>
+  <dimension ref="A1:Q66"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -12251,9 +12349,10 @@
     <col min="12" max="12" width="7.77734375" customWidth="1"/>
     <col min="13" max="14" width="9.109375" customWidth="1"/>
     <col min="15" max="15" width="7.5546875" customWidth="1"/>
+    <col min="16" max="16" width="7.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -12296,12 +12395,15 @@
       <c r="O1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="P1" s="3">
-        <f>AVERAGE(N2:N35)</f>
-        <v>1.0096136059080856</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q1" s="3">
+        <f>AVERAGE(N2:N66)</f>
+        <v>1.0177618312809802</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -12343,15 +12445,19 @@
         <v>0.9827499999999979</v>
       </c>
       <c r="O2" s="4">
-        <f>STANDARDIZE(N2,P$1,P$2)</f>
-        <v>-1.5771752669169647</v>
-      </c>
-      <c r="P2" s="3">
-        <f>_xlfn.STDEV.S(N2:N35)</f>
-        <v>1.7032733439068058E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+        <f>STANDARDIZE(N2,Q$1,Q$2)</f>
+        <v>-2.0659110372486018</v>
+      </c>
+      <c r="P2" s="2">
+        <f>N2-Q$1</f>
+        <v>-3.5011831280982286E-2</v>
+      </c>
+      <c r="Q2" s="3">
+        <f>_xlfn.STDEV.S(N2:N66)</f>
+        <v>1.694740511557136E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -12393,11 +12499,15 @@
         <v>0.9725416666666663</v>
       </c>
       <c r="O3" s="4">
-        <f t="shared" ref="O3:O35" si="1">STANDARDIZE(N3,P$1,P$2)</f>
-        <v>-2.1765114433357593</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+        <f>STANDARDIZE(N3,Q$1,Q$2)</f>
+        <v>-2.6682648054931648</v>
+      </c>
+      <c r="P3" s="2">
+        <f t="shared" ref="P3:P66" si="1">N3-Q$1</f>
+        <v>-4.5220164614313885E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -12439,11 +12549,15 @@
         <v>0.97387499999999949</v>
       </c>
       <c r="O4" s="4">
+        <f>STANDARDIZE(N4,Q$1,Q$2)</f>
+        <v>-2.5895900275999928</v>
+      </c>
+      <c r="P4" s="2">
         <f t="shared" si="1"/>
-        <v>-2.0982307998851368</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+        <v>-4.3886831280980698E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -12485,11 +12599,15 @@
         <v>0.9893541666666662</v>
       </c>
       <c r="O5" s="4">
+        <f>STANDARDIZE(N5,Q$1,Q$2)</f>
+        <v>-1.676225027996344</v>
+      </c>
+      <c r="P5" s="2">
         <f t="shared" si="1"/>
-        <v>-1.1894414548254602</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+        <v>-2.8407664614313988E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -12531,11 +12649,15 @@
         <v>1.0017708333333313</v>
       </c>
       <c r="O6" s="4">
+        <f>STANDARDIZE(N6,Q$1,Q$2)</f>
+        <v>-0.94356615886619133</v>
+      </c>
+      <c r="P6" s="2">
         <f t="shared" si="1"/>
-        <v>-0.46045296269154867</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+        <v>-1.5990997947648911E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -12577,11 +12699,15 @@
         <v>1.000437499999999</v>
       </c>
       <c r="O7" s="4">
+        <f>STANDARDIZE(N7,Q$1,Q$2)</f>
+        <v>-1.022240936759311</v>
+      </c>
+      <c r="P7" s="2">
         <f t="shared" si="1"/>
-        <v>-0.53873360614211929</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+        <v>-1.7324331280981209E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -12623,11 +12749,15 @@
         <v>0.99220833333333225</v>
       </c>
       <c r="O8" s="4">
+        <f>STANDARDIZE(N8,Q$1,Q$2)</f>
+        <v>-1.5078118315687905</v>
+      </c>
+      <c r="P8" s="2">
         <f t="shared" si="1"/>
-        <v>-1.0218719524389888</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+        <v>-2.5553497947647941E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -12669,11 +12799,15 @@
         <v>1.0033541666666641</v>
       </c>
       <c r="O9" s="4">
+        <f>STANDARDIZE(N9,Q$1,Q$2)</f>
+        <v>-0.85013986011806908</v>
+      </c>
+      <c r="P9" s="2">
         <f t="shared" si="1"/>
-        <v>-0.36749469859395367</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+        <v>-1.4407664614316085E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -12715,11 +12849,15 @@
         <v>1.0081666666666633</v>
       </c>
       <c r="O10" s="4">
+        <f>STANDARDIZE(N10,Q$1,Q$2)</f>
+        <v>-0.56617308365991559</v>
+      </c>
+      <c r="P10" s="2">
         <f t="shared" si="1"/>
-        <v>-8.4950501139376744E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+        <v>-9.5951646143168645E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -12761,11 +12899,15 @@
         <v>1.0100833333333323</v>
       </c>
       <c r="O11" s="4">
+        <f>STANDARDIZE(N11,Q$1,Q$2)</f>
+        <v>-0.45307809043832992</v>
+      </c>
+      <c r="P11" s="2">
         <f t="shared" si="1"/>
-        <v>2.7577923821043408E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+        <v>-7.6784979476478554E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -12807,11 +12949,15 @@
         <v>1.0036874999999972</v>
       </c>
       <c r="O12" s="4">
+        <f>STANDARDIZE(N12,Q$1,Q$2)</f>
+        <v>-0.83047116564478918</v>
+      </c>
+      <c r="P12" s="2">
         <f t="shared" si="1"/>
-        <v>-0.34792453773131099</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+        <v>-1.407433128098301E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -12853,11 +12999,15 @@
         <v>1.0071041666666625</v>
       </c>
       <c r="O13" s="4">
+        <f>STANDARDIZE(N13,Q$1,Q$2)</f>
+        <v>-0.62886704729359444</v>
+      </c>
+      <c r="P13" s="2">
         <f t="shared" si="1"/>
-        <v>-0.14733038888914882</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+        <v>-1.0657664614317719E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -12899,11 +13049,15 @@
         <v>1.0061874999999958</v>
       </c>
       <c r="O14" s="4">
+        <f>STANDARDIZE(N14,Q$1,Q$2)</f>
+        <v>-0.68295595709515688</v>
+      </c>
+      <c r="P14" s="2">
         <f t="shared" si="1"/>
-        <v>-0.20114833126145848</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+        <v>-1.1574331280984396E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -12945,11 +13099,15 @@
         <v>1.0031874999999975</v>
       </c>
       <c r="O15" s="4">
+        <f>STANDARDIZE(N15,Q$1,Q$2)</f>
+        <v>-0.85997420735471564</v>
+      </c>
+      <c r="P15" s="2">
         <f t="shared" si="1"/>
-        <v>-0.37727977902528154</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+        <v>-1.4574331280982733E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -12991,11 +13149,15 @@
         <v>0.997270833333329</v>
       </c>
       <c r="O16" s="4">
+        <f>STANDARDIZE(N16,Q$1,Q$2)</f>
+        <v>-1.2090935342558111</v>
+      </c>
+      <c r="P16" s="2">
         <f t="shared" si="1"/>
-        <v>-0.72465013433756353</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+        <v>-2.0490997947651191E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -13037,11 +13199,15 @@
         <v>1.0057083333333301</v>
       </c>
       <c r="O17" s="4">
+        <f>STANDARDIZE(N17,Q$1,Q$2)</f>
+        <v>-0.7112297054004616</v>
+      </c>
+      <c r="P17" s="2">
         <f t="shared" si="1"/>
-        <v>-0.22928043750147228</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+        <v>-1.2053497947650094E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -13083,11 +13249,15 @@
         <v>1.0278958333333275</v>
       </c>
       <c r="O18" s="4">
+        <f>STANDARDIZE(N18,Q$1,Q$2)</f>
+        <v>0.59796777047809502</v>
+      </c>
+      <c r="P18" s="2">
         <f t="shared" si="1"/>
-        <v>1.073358394919036</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+        <v>1.0134002052347268E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -13129,11 +13299,15 @@
         <v>0.99983333333333224</v>
       </c>
       <c r="O19" s="4">
+        <f>STANDARDIZE(N19,Q$1,Q$2)</f>
+        <v>-1.0578904454921629</v>
+      </c>
+      <c r="P19" s="2">
         <f t="shared" si="1"/>
-        <v>-0.57420452270569089</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+        <v>-1.7928497947647948E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -13175,11 +13349,15 @@
         <v>0.98558333333333203</v>
       </c>
       <c r="O20" s="4">
+        <f>STANDARDIZE(N20,Q$1,Q$2)</f>
+        <v>-1.8987271342255452</v>
+      </c>
+      <c r="P20" s="2">
         <f t="shared" si="1"/>
-        <v>-1.4108288995843261</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+        <v>-3.2178497947648155E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -13221,11 +13399,15 @@
         <v>1.0283124999999949</v>
       </c>
       <c r="O21" s="4">
+        <f>STANDARDIZE(N21,Q$1,Q$2)</f>
+        <v>0.62255363856975721</v>
+      </c>
+      <c r="P21" s="2">
         <f t="shared" si="1"/>
-        <v>1.0978210959974013</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+        <v>1.0550668719014666E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -13267,11 +13449,15 @@
         <v>1.0262916666666639</v>
       </c>
       <c r="O22" s="4">
+        <f>STANDARDIZE(N22,Q$1,Q$2)</f>
+        <v>0.50331217832554753</v>
+      </c>
+      <c r="P22" s="2">
         <f t="shared" si="1"/>
-        <v>0.9791769957676798</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+        <v>8.5298353856837483E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -13313,11 +13499,15 @@
         <v>1.0216041666666633</v>
       </c>
       <c r="O23" s="4">
+        <f>STANDARDIZE(N23,Q$1,Q$2)</f>
+        <v>0.22672116229479697</v>
+      </c>
+      <c r="P23" s="2">
         <f t="shared" si="1"/>
-        <v>0.70397160863651731</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+        <v>3.8423353856831266E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -13359,11 +13549,15 @@
         <v>1.0191666666666626</v>
       </c>
       <c r="O24" s="4">
+        <f>STANDARDIZE(N24,Q$1,Q$2)</f>
+        <v>8.2893833958780999E-2</v>
+      </c>
+      <c r="P24" s="2">
         <f t="shared" si="1"/>
-        <v>0.56086480732828725</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+        <v>1.4048353856823681E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -13405,11 +13599,15 @@
         <v>1.0101041666666646</v>
       </c>
       <c r="O25" s="4">
+        <f>STANDARDIZE(N25,Q$1,Q$2)</f>
+        <v>-0.45184879703381298</v>
+      </c>
+      <c r="P25" s="2">
         <f t="shared" si="1"/>
-        <v>2.8801058874895837E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+        <v>-7.6576646143156069E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -13451,11 +13649,15 @@
         <v>1.0245624999999965</v>
       </c>
       <c r="O26" s="4">
+        <f>STANDARDIZE(N26,Q$1,Q$2)</f>
+        <v>0.40128082574528251</v>
+      </c>
+      <c r="P26" s="2">
         <f t="shared" si="1"/>
-        <v>0.87765678629259636</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+        <v>6.8006687190163007E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>4</v>
       </c>
@@ -13497,11 +13699,15 @@
         <v>1.0401041666666651</v>
       </c>
       <c r="O27" s="4">
+        <f>STANDARDIZE(N27,Q$1,Q$2)</f>
+        <v>1.3183337055627835</v>
+      </c>
+      <c r="P27" s="2">
         <f t="shared" si="1"/>
-        <v>1.7901155365141299</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+        <v>2.2342335385684864E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>4</v>
       </c>
@@ -13543,11 +13749,15 @@
         <v>1.0390416666666649</v>
       </c>
       <c r="O28" s="4">
+        <f>STANDARDIZE(N28,Q$1,Q$2)</f>
+        <v>1.2556397419291438</v>
+      </c>
+      <c r="P28" s="2">
         <f t="shared" si="1"/>
-        <v>1.7277356487643969</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+        <v>2.1279835385684676E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>4</v>
       </c>
@@ -13589,11 +13799,15 @@
         <v>1.0333468589374948</v>
       </c>
       <c r="O29" s="4">
+        <f>STANDARDIZE(N29,Q$1,Q$2)</f>
+        <v>0.91961144200152467</v>
+      </c>
+      <c r="P29" s="2">
         <f t="shared" si="1"/>
-        <v>1.3933907387390998</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+        <v>1.5585027656514594E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>4</v>
       </c>
@@ -13635,11 +13849,15 @@
         <v>1.0173815951666656</v>
       </c>
       <c r="O30" s="4">
+        <f>STANDARDIZE(N30,Q$1,Q$2)</f>
+        <v>-2.2436243880499956E-2</v>
+      </c>
+      <c r="P30" s="2">
         <f t="shared" si="1"/>
-        <v>0.45606239810942789</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+        <v>-3.8023611431459159E-4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>4</v>
       </c>
@@ -13681,11 +13899,15 @@
         <v>1.0213693587083308</v>
       </c>
       <c r="O31" s="4">
+        <f>STANDARDIZE(N31,Q$1,Q$2)</f>
+        <v>0.2128660643177748</v>
+      </c>
+      <c r="P31" s="2">
         <f t="shared" si="1"/>
-        <v>0.69018592008731783</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+        <v>3.6075274273505986E-3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>4</v>
       </c>
@@ -13727,11 +13949,15 @@
         <v>1.0182929276874972</v>
       </c>
       <c r="O32" s="4">
+        <f>STANDARDIZE(N32,Q$1,Q$2)</f>
+        <v>3.133791886694659E-2</v>
+      </c>
+      <c r="P32" s="2">
         <f t="shared" si="1"/>
-        <v>0.50956717020556808</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+        <v>5.3109640651705092E-4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>4</v>
       </c>
@@ -13773,11 +13999,15 @@
         <v>1.023453438874995</v>
       </c>
       <c r="O33" s="4">
+        <f>STANDARDIZE(N33,Q$1,Q$2)</f>
+        <v>0.33583947248568996</v>
+      </c>
+      <c r="P33" s="2">
         <f t="shared" si="1"/>
-        <v>0.81254327242419555</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+        <v>5.6916075940147692E-3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>4</v>
       </c>
@@ -13819,11 +14049,15 @@
         <v>1.0127342579166652</v>
       </c>
       <c r="O34" s="4">
+        <f>STANDARDIZE(N34,Q$1,Q$2)</f>
+        <v>-0.29665741333436768</v>
+      </c>
+      <c r="P34" s="2">
         <f t="shared" si="1"/>
-        <v>0.18321498541283629</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+        <v>-5.02757336431503E-3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>4</v>
       </c>
@@ -13865,11 +14099,15 @@
         <v>1.0200966635833333</v>
       </c>
       <c r="O35" s="4">
+        <f>STANDARDIZE(N35,Q$1,Q$2)</f>
+        <v>0.1377693096040904</v>
+      </c>
+      <c r="P35" s="2">
         <f t="shared" si="1"/>
-        <v>0.61546537511135313</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+        <v>2.3348323023530959E-3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="D36" t="s">
         <v>5</v>
       </c>
@@ -13901,8 +14139,12 @@
         <f t="shared" si="0"/>
         <v>1.0432222222222201</v>
       </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P36" s="2">
+        <f t="shared" si="1"/>
+        <v>2.5460390941239863E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="D37" t="s">
         <v>5</v>
       </c>
@@ -13934,8 +14176,12 @@
         <f t="shared" si="0"/>
         <v>1.02322222222222</v>
       </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P37" s="2">
+        <f t="shared" si="1"/>
+        <v>5.4603909412398455E-3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="D38" t="s">
         <v>5</v>
       </c>
@@ -13967,8 +14213,12 @@
         <f t="shared" si="0"/>
         <v>1.0366944444444399</v>
       </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P38" s="2">
+        <f t="shared" si="1"/>
+        <v>1.8932613163459733E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="D39" t="s">
         <v>5</v>
       </c>
@@ -14000,8 +14250,12 @@
         <f t="shared" si="0"/>
         <v>1.0418333333333301</v>
       </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P39" s="2">
+        <f t="shared" si="1"/>
+        <v>2.4071502052349869E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="D40" t="s">
         <v>5</v>
       </c>
@@ -14033,8 +14287,12 @@
         <f t="shared" si="0"/>
         <v>1.0279999999999987</v>
       </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P40" s="2">
+        <f t="shared" si="1"/>
+        <v>1.0238168719018503E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="D41" t="s">
         <v>5</v>
       </c>
@@ -14066,8 +14324,12 @@
         <f t="shared" si="0"/>
         <v>1.0332777777777744</v>
       </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P41" s="2">
+        <f t="shared" si="1"/>
+        <v>1.551594649679422E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
       <c r="D42" t="s">
         <v>5</v>
       </c>
@@ -14099,8 +14361,12 @@
         <f t="shared" si="0"/>
         <v>1.0329444444444433</v>
       </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P42" s="2">
+        <f t="shared" si="1"/>
+        <v>1.5182613163463143E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="D43" t="s">
         <v>5</v>
       </c>
@@ -14132,8 +14398,12 @@
         <f t="shared" si="0"/>
         <v>1.0113888888888869</v>
       </c>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P43" s="2">
+        <f t="shared" si="1"/>
+        <v>-6.3729423920932948E-3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="D44" t="s">
         <v>5</v>
       </c>
@@ -14165,8 +14435,12 @@
         <f t="shared" si="0"/>
         <v>1.0190555555555501</v>
       </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P44" s="2">
+        <f t="shared" si="1"/>
+        <v>1.2937242745698629E-3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="D45" t="s">
         <v>5</v>
       </c>
@@ -14198,8 +14472,12 @@
         <f t="shared" si="0"/>
         <v>1.0101666666666633</v>
       </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P45" s="2">
+        <f t="shared" si="1"/>
+        <v>-7.5951646143168627E-3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="D46" t="s">
         <v>5</v>
       </c>
@@ -14231,8 +14509,12 @@
         <f t="shared" si="0"/>
         <v>1.0155277777777776</v>
       </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P46" s="2">
+        <f t="shared" si="1"/>
+        <v>-2.2340535032026043E-3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
       <c r="D47" t="s">
         <v>5</v>
       </c>
@@ -14264,8 +14546,12 @@
         <f t="shared" si="0"/>
         <v>1.0228333333333299</v>
       </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P47" s="2">
+        <f t="shared" si="1"/>
+        <v>5.0715020523497412E-3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
       <c r="D48" t="s">
         <v>5</v>
       </c>
@@ -14297,8 +14583,12 @@
         <f t="shared" si="0"/>
         <v>1.0286944444444435</v>
       </c>
-    </row>
-    <row r="49" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="P48" s="2">
+        <f t="shared" si="1"/>
+        <v>1.0932613163463278E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D49" t="s">
         <v>5</v>
       </c>
@@ -14330,8 +14620,12 @@
         <f t="shared" si="0"/>
         <v>1.0189444444444422</v>
       </c>
-    </row>
-    <row r="50" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="P49" s="2">
+        <f t="shared" si="1"/>
+        <v>1.1826131634620207E-3</v>
+      </c>
+    </row>
+    <row r="50" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D50" t="s">
         <v>5</v>
       </c>
@@ -14363,8 +14657,12 @@
         <f t="shared" si="0"/>
         <v>1.02044444444444</v>
       </c>
-    </row>
-    <row r="51" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="P50" s="2">
+        <f t="shared" si="1"/>
+        <v>2.6826131634598571E-3</v>
+      </c>
+    </row>
+    <row r="51" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D51" t="s">
         <v>5</v>
       </c>
@@ -14396,8 +14694,12 @@
         <f t="shared" si="0"/>
         <v>1.0211944444444399</v>
       </c>
-    </row>
-    <row r="52" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="P51" s="2">
+        <f t="shared" si="1"/>
+        <v>3.4326131634596635E-3</v>
+      </c>
+    </row>
+    <row r="52" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D52" t="s">
         <v>5</v>
       </c>
@@ -14429,8 +14731,12 @@
         <f t="shared" si="0"/>
         <v>1.0051944444444429</v>
       </c>
-    </row>
-    <row r="53" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="P52" s="2">
+        <f t="shared" si="1"/>
+        <v>-1.2567386836537242E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D53" t="s">
         <v>5</v>
       </c>
@@ -14462,8 +14768,12 @@
         <f t="shared" si="0"/>
         <v>1.0075277777777754</v>
       </c>
-    </row>
-    <row r="54" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="P53" s="2">
+        <f t="shared" si="1"/>
+        <v>-1.0234053503204832E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D54" t="s">
         <v>5</v>
       </c>
@@ -14495,8 +14805,12 @@
         <f t="shared" si="0"/>
         <v>1.0187499999999967</v>
       </c>
-    </row>
-    <row r="55" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="P54" s="2">
+        <f t="shared" si="1"/>
+        <v>9.8816871901652448E-4</v>
+      </c>
+    </row>
+    <row r="55" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D55" t="s">
         <v>5</v>
       </c>
@@ -14528,8 +14842,12 @@
         <f t="shared" si="0"/>
         <v>1.0202499999999965</v>
       </c>
-    </row>
-    <row r="56" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="P55" s="2">
+        <f t="shared" si="1"/>
+        <v>2.4881687190163593E-3</v>
+      </c>
+    </row>
+    <row r="56" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D56" t="s">
         <v>5</v>
       </c>
@@ -14561,8 +14879,12 @@
         <f t="shared" si="0"/>
         <v>1.0256944444444434</v>
       </c>
-    </row>
-    <row r="57" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="P56" s="2">
+        <f t="shared" si="1"/>
+        <v>7.9326131634631647E-3</v>
+      </c>
+    </row>
+    <row r="57" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D57" t="s">
         <v>5</v>
       </c>
@@ -14594,8 +14916,12 @@
         <f t="shared" si="0"/>
         <v>1.0322222222222199</v>
       </c>
-    </row>
-    <row r="58" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="P57" s="2">
+        <f t="shared" si="1"/>
+        <v>1.4460390941239742E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D58" t="s">
         <v>5</v>
       </c>
@@ -14627,8 +14953,12 @@
         <f t="shared" si="0"/>
         <v>1.0246666666666633</v>
       </c>
-    </row>
-    <row r="59" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="P58" s="2">
+        <f t="shared" si="1"/>
+        <v>6.9048353856830946E-3</v>
+      </c>
+    </row>
+    <row r="59" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D59" t="s">
         <v>5</v>
       </c>
@@ -14660,8 +14990,12 @@
         <f t="shared" si="0"/>
         <v>1.0240277777777733</v>
       </c>
-    </row>
-    <row r="60" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="P59" s="2">
+        <f t="shared" si="1"/>
+        <v>6.2659464967931289E-3</v>
+      </c>
+    </row>
+    <row r="60" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D60" t="s">
         <v>5</v>
       </c>
@@ -14693,8 +15027,12 @@
         <f t="shared" si="0"/>
         <v>1.0192499999999967</v>
       </c>
-    </row>
-    <row r="61" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="P60" s="2">
+        <f t="shared" si="1"/>
+        <v>1.4881687190164694E-3</v>
+      </c>
+    </row>
+    <row r="61" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D61" t="s">
         <v>5</v>
       </c>
@@ -14726,8 +15064,12 @@
         <f t="shared" si="0"/>
         <v>1.0478333333333301</v>
       </c>
-    </row>
-    <row r="62" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="P61" s="2">
+        <f t="shared" si="1"/>
+        <v>3.0071502052349874E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D62" t="s">
         <v>5</v>
       </c>
@@ -14759,8 +15101,12 @@
         <f t="shared" si="0"/>
         <v>1.0421944444444433</v>
       </c>
-    </row>
-    <row r="63" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="P62" s="2">
+        <f t="shared" si="1"/>
+        <v>2.4432613163463124E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D63" t="s">
         <v>5</v>
       </c>
@@ -14792,8 +15138,12 @@
         <f t="shared" si="0"/>
         <v>1.0393508768333266</v>
       </c>
-    </row>
-    <row r="64" spans="4:14" x14ac:dyDescent="0.3">
+      <c r="P63" s="2">
+        <f t="shared" si="1"/>
+        <v>2.158904555234642E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="4:16" x14ac:dyDescent="0.3">
       <c r="G64" t="s">
         <v>6</v>
       </c>
@@ -14816,8 +15166,12 @@
         <f t="shared" si="0"/>
         <v>1.0269166666666649</v>
       </c>
-    </row>
-    <row r="65" spans="7:14" x14ac:dyDescent="0.3">
+      <c r="P64" s="2">
+        <f t="shared" si="1"/>
+        <v>9.1548353856847342E-3</v>
+      </c>
+    </row>
+    <row r="65" spans="7:16" x14ac:dyDescent="0.3">
       <c r="G65" t="s">
         <v>6</v>
       </c>
@@ -14840,8 +15194,12 @@
         <f t="shared" si="0"/>
         <v>1.0355833333333302</v>
       </c>
-    </row>
-    <row r="66" spans="7:14" x14ac:dyDescent="0.3">
+      <c r="P65" s="2">
+        <f t="shared" si="1"/>
+        <v>1.7821502052350002E-2</v>
+      </c>
+    </row>
+    <row r="66" spans="7:16" x14ac:dyDescent="0.3">
       <c r="G66" t="s">
         <v>6</v>
       </c>
@@ -14863,6 +15221,10 @@
       <c r="N66" s="2">
         <f t="shared" si="0"/>
         <v>1.050749999999995</v>
+      </c>
+      <c r="P66" s="2">
+        <f t="shared" si="1"/>
+        <v>3.2988168719014777E-2</v>
       </c>
     </row>
   </sheetData>
@@ -14872,13 +15234,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D450D66-8CE6-424E-B1F2-F32778C5AA83}">
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:V36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="6.5546875" customWidth="1"/>
+    <col min="3" max="3" width="7.21875" customWidth="1"/>
+    <col min="4" max="4" width="6.5546875" customWidth="1"/>
+    <col min="5" max="5" width="7.88671875" customWidth="1"/>
+    <col min="6" max="6" width="6.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -14886,439 +15251,859 @@
         <v>9</v>
       </c>
       <c r="C1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="4">
+      <c r="E1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="4">
         <f>AVERAGE(B2:B36)</f>
-        <v>362.07249999999993</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+        <v>365.18504901960779</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2015</v>
       </c>
       <c r="B2" s="3">
         <v>259.74166666666667</v>
       </c>
-      <c r="C2" s="4">
-        <f>STANDARDIZE(B2,D$1,D$2)</f>
-        <v>-1.0404239729056239</v>
+      <c r="C2" s="3">
+        <f>B2-F$1</f>
+        <v>-105.44338235294111</v>
       </c>
       <c r="D2" s="4">
+        <f>STANDARDIZE(B2,F$1,F$2)</f>
+        <v>-1.0751984741460796</v>
+      </c>
+      <c r="E2" s="5">
+        <v>-2.0659110372486018</v>
+      </c>
+      <c r="F2" s="4">
         <f>_xlfn.STDEV.S(B2:B36)</f>
-        <v>98.354936062796398</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+        <v>98.068761152850442</v>
+      </c>
+      <c r="O2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2014</v>
       </c>
       <c r="B3" s="3">
         <v>326.30833333333334</v>
       </c>
-      <c r="C3" s="4">
-        <f t="shared" ref="C3:C36" si="0">STANDARDIZE(B3,D$1,D$2)</f>
-        <v>-0.36362350582824182</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C3" s="3">
+        <f t="shared" ref="C3:C35" si="0">B3-F$1</f>
+        <v>-38.876715686274451</v>
+      </c>
+      <c r="D3" s="4">
+        <f>STANDARDIZE(B3,F$1,F$2)</f>
+        <v>-0.39642303246475213</v>
+      </c>
+      <c r="E3" s="5">
+        <v>-2.6682648054931648</v>
+      </c>
+      <c r="O3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2013</v>
       </c>
       <c r="B4" s="3">
         <v>294.05</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="3">
         <f t="shared" si="0"/>
-        <v>-0.69160230002660761</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+        <v>-71.135049019607777</v>
+      </c>
+      <c r="D4" s="4">
+        <f>STANDARDIZE(B4,F$1,F$2)</f>
+        <v>-0.72535890311427864</v>
+      </c>
+      <c r="E4" s="5">
+        <v>-2.5895900275999928</v>
+      </c>
+      <c r="O4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2012</v>
       </c>
       <c r="B5" s="3">
         <v>356.47499999999997</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="3">
         <f t="shared" si="0"/>
-        <v>-5.6911226056068485E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+        <v>-8.7100490196078226</v>
+      </c>
+      <c r="D5" s="4">
+        <f>STANDARDIZE(B5,F$1,F$2)</f>
+        <v>-8.8815734156489426E-2</v>
+      </c>
+      <c r="E5" s="5">
+        <v>-1.676225027996344</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2011</v>
       </c>
       <c r="B6" s="3">
         <v>515.89166666666677</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="3">
         <f t="shared" si="0"/>
-        <v>1.5639191363863867</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+        <v>150.70661764705898</v>
+      </c>
+      <c r="D6" s="4">
+        <f>STANDARDIZE(B6,F$1,F$2)</f>
+        <v>1.5367443809366259</v>
+      </c>
+      <c r="E6" s="5">
+        <v>-0.94356615886619133</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2010</v>
       </c>
       <c r="B7" s="3">
         <v>465.34166666666653</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="3">
         <f t="shared" si="0"/>
-        <v>1.0499642498952226</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+        <v>100.15661764705874</v>
+      </c>
+      <c r="D7" s="4">
+        <f>STANDARDIZE(B7,F$1,F$2)</f>
+        <v>1.0212897202907882</v>
+      </c>
+      <c r="E7" s="5">
+        <v>-1.022240936759311</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2009</v>
       </c>
       <c r="B8" s="3">
         <v>419.25833333333338</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="3">
         <f t="shared" si="0"/>
-        <v>0.58142311532613034</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+        <v>54.073284313725594</v>
+      </c>
+      <c r="D8" s="4">
+        <f>STANDARDIZE(B8,F$1,F$2)</f>
+        <v>0.5513813336486092</v>
+      </c>
+      <c r="E8" s="5">
+        <v>-1.5078118315687905</v>
+      </c>
+      <c r="O8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>2008</v>
       </c>
       <c r="B9" s="3">
         <v>560.5</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="3">
         <f t="shared" si="0"/>
-        <v>2.0174635655633044</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+        <v>195.31495098039221</v>
+      </c>
+      <c r="D9" s="4">
+        <f>STANDARDIZE(B9,F$1,F$2)</f>
+        <v>1.9916123002305841</v>
+      </c>
+      <c r="E9" s="5">
+        <v>-0.85013986011806908</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2007</v>
       </c>
       <c r="B10" s="3">
         <v>512.25833333333333</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="3">
         <f t="shared" si="0"/>
-        <v>1.5269780993751516</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+        <v>147.07328431372554</v>
+      </c>
+      <c r="D10" s="4">
+        <f>STANDARDIZE(B10,F$1,F$2)</f>
+        <v>1.4996955461127566</v>
+      </c>
+      <c r="E10" s="5">
+        <v>-0.56617308365991559</v>
+      </c>
+      <c r="O10" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="P10" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="R10" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="S10" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="T10" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="U10" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="V10" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2006</v>
       </c>
       <c r="B11" s="3">
         <v>482.4083333333333</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="3">
         <f t="shared" si="0"/>
-        <v>1.2234854512690942</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+        <v>117.22328431372551</v>
+      </c>
+      <c r="D11" s="4">
+        <f>STANDARDIZE(B11,F$1,F$2)</f>
+        <v>1.195317274692812</v>
+      </c>
+      <c r="E11" s="5">
+        <v>-0.45307809043832992</v>
+      </c>
+      <c r="O11" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="P11" s="10">
+        <v>34</v>
+      </c>
+      <c r="Q11" s="10">
+        <v>0</v>
+      </c>
+      <c r="R11" s="10">
+        <v>34</v>
+      </c>
+      <c r="S11" s="12">
+        <v>-2.1226778018383334</v>
+      </c>
+      <c r="T11" s="12">
+        <v>1.9916123002305841</v>
+      </c>
+      <c r="U11" s="12">
+        <v>5.4817261840867104E-16</v>
+      </c>
+      <c r="V11" s="12">
+        <v>0.99999999999999678</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>2005</v>
       </c>
       <c r="B12" s="3">
         <v>401.79999999999995</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="3">
         <f t="shared" si="0"/>
-        <v>0.40391973794416697</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+        <v>36.614950980392166</v>
+      </c>
+      <c r="D12" s="4">
+        <f>STANDARDIZE(B12,F$1,F$2)</f>
+        <v>0.37335998283208582</v>
+      </c>
+      <c r="E12" s="5">
+        <v>-0.83047116564478918</v>
+      </c>
+      <c r="O12" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="P12" s="11">
+        <v>34</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>0</v>
+      </c>
+      <c r="R12" s="11">
+        <v>34</v>
+      </c>
+      <c r="S12" s="13">
+        <v>-2.6682648054931648</v>
+      </c>
+      <c r="T12" s="13">
+        <v>1.3183337055627835</v>
+      </c>
+      <c r="U12" s="13">
+        <v>-0.4807948660770418</v>
+      </c>
+      <c r="V12" s="13">
+        <v>1.0050348901743253</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2004</v>
       </c>
       <c r="B13" s="3">
         <v>370.78333333333336</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="3">
         <f t="shared" si="0"/>
-        <v>8.8565288962943814E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+        <v>5.5982843137255713</v>
+      </c>
+      <c r="D13" s="4">
+        <f>STANDARDIZE(B13,F$1,F$2)</f>
+        <v>5.7085296560441492E-2</v>
+      </c>
+      <c r="E13" s="5">
+        <v>-0.62886704729359444</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2003</v>
       </c>
       <c r="B14" s="3">
         <v>366.98333333333335</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="3">
         <f t="shared" si="0"/>
-        <v>4.9929708969542803E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1.79828431372556</v>
+      </c>
+      <c r="D14" s="4">
+        <f>STANDARDIZE(B14,F$1,F$2)</f>
+        <v>1.833697390061597E-2</v>
+      </c>
+      <c r="E14" s="5">
+        <v>-0.68295595709515688</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2002</v>
       </c>
       <c r="B15" s="3">
         <v>361.55833333333334</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="3">
         <f t="shared" si="0"/>
-        <v>-5.2276650999835781E-3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+        <v>-3.6267156862744514</v>
+      </c>
+      <c r="D15" s="4">
+        <f>STANDARDIZE(B15,F$1,F$2)</f>
+        <v>-3.6981355159792777E-2</v>
+      </c>
+      <c r="E15" s="5">
+        <v>-0.85997420735471564</v>
+      </c>
+      <c r="O15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>2001</v>
       </c>
       <c r="B16" s="3">
         <v>284.84999999999997</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="3">
         <f t="shared" si="0"/>
-        <v>-0.78514107264221022</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+        <v>-80.335049019607823</v>
+      </c>
+      <c r="D16" s="4">
+        <f>STANDARDIZE(B16,F$1,F$2)</f>
+        <v>-0.81917063165911952</v>
+      </c>
+      <c r="E16" s="5">
+        <v>-1.2090935342558111</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2000</v>
       </c>
       <c r="B17" s="3">
         <v>511.77500000000003</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="3">
         <f t="shared" si="0"/>
-        <v>1.5220639247268686</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+        <v>146.58995098039225</v>
+      </c>
+      <c r="D17" s="4">
+        <f>STANDARDIZE(B17,F$1,F$2)</f>
+        <v>1.4947670313884811</v>
+      </c>
+      <c r="E17" s="5">
+        <v>-0.7112297054004616</v>
+      </c>
+      <c r="O17" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="P17" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q17" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>1999</v>
       </c>
       <c r="B18" s="3">
         <v>537.83333333333337</v>
       </c>
-      <c r="C18" s="4">
+      <c r="C18" s="3">
         <f t="shared" si="0"/>
-        <v>1.7870057199886329</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+        <v>172.64828431372558</v>
+      </c>
+      <c r="D18" s="4">
+        <f>STANDARDIZE(B18,F$1,F$2)</f>
+        <v>1.7604819545403978</v>
+      </c>
+      <c r="E18" s="5">
+        <v>0.59796777047809502</v>
+      </c>
+      <c r="O18" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="P18" s="15">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="12">
+        <v>0.1022248488675736</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>1998</v>
       </c>
       <c r="B19" s="3">
         <v>358.34166666666664</v>
       </c>
-      <c r="C19" s="4">
+      <c r="C19" s="3">
         <f t="shared" si="0"/>
-        <v>-3.7932344655801302E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+        <v>-6.8433823529411484</v>
+      </c>
+      <c r="D19" s="4">
+        <f>STANDARDIZE(B19,F$1,F$2)</f>
+        <v>-6.97814703937681E-2</v>
+      </c>
+      <c r="E19" s="5">
+        <v>-1.0578904454921629</v>
+      </c>
+      <c r="O19" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="P19" s="13">
+        <v>0.1022248488675736</v>
+      </c>
+      <c r="Q19" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>1997</v>
       </c>
       <c r="B20" s="3">
         <v>214.61666666666665</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C20" s="3">
         <f t="shared" si="0"/>
-        <v>-1.4992214853272599</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+        <v>-150.56838235294114</v>
+      </c>
+      <c r="D20" s="4">
+        <f>STANDARDIZE(B20,F$1,F$2)</f>
+        <v>-1.5353348057315064</v>
+      </c>
+      <c r="E20" s="5">
+        <v>-1.8987271342255452</v>
+      </c>
+      <c r="O20" s="18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>1996</v>
       </c>
       <c r="B21" s="3">
         <v>407.42499999999995</v>
       </c>
-      <c r="C21" s="4">
+      <c r="C21" s="3">
         <f t="shared" si="0"/>
-        <v>0.4611105635922933</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+        <v>42.239950980392166</v>
+      </c>
+      <c r="D21" s="4">
+        <f>STANDARDIZE(B21,F$1,F$2)</f>
+        <v>0.43071769729564319</v>
+      </c>
+      <c r="E21" s="5">
+        <v>0.62255363856975721</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>1995</v>
       </c>
       <c r="B22" s="3">
         <v>391.52500000000003</v>
       </c>
-      <c r="C22" s="4">
+      <c r="C22" s="3">
         <f t="shared" si="0"/>
-        <v>0.29945116309359038</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+        <v>26.339950980392246</v>
+      </c>
+      <c r="D22" s="4">
+        <f>STANDARDIZE(B22,F$1,F$2)</f>
+        <v>0.26858655774532192</v>
+      </c>
+      <c r="E22" s="5">
+        <v>0.50331217832554753</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>1994</v>
       </c>
       <c r="B23" s="3">
         <v>384.99999999999994</v>
       </c>
-      <c r="C23" s="4">
+      <c r="C23" s="3">
         <f t="shared" si="0"/>
-        <v>0.23310980534176295</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+        <v>19.814950980392155</v>
+      </c>
+      <c r="D23" s="4">
+        <f>STANDARDIZE(B23,F$1,F$2)</f>
+        <v>0.20205160896759444</v>
+      </c>
+      <c r="E23" s="5">
+        <v>0.22672116229479697</v>
+      </c>
+      <c r="O23" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>1993</v>
       </c>
       <c r="B24" s="3">
         <v>324.16666666666669</v>
       </c>
-      <c r="C24" s="4">
+      <c r="C24" s="3">
         <f t="shared" si="0"/>
-        <v>-0.38539838314908381</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+        <v>-41.018382352941103</v>
+      </c>
+      <c r="D24" s="4">
+        <f>STANDARDIZE(B24,F$1,F$2)</f>
+        <v>-0.41826145115680269</v>
+      </c>
+      <c r="E24" s="5">
+        <v>8.2893833958780999E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>1992</v>
       </c>
       <c r="B25" s="3">
         <v>248.8416666666667</v>
       </c>
-      <c r="C25" s="4">
+      <c r="C25" s="3">
         <f t="shared" si="0"/>
-        <v>-1.1512470839393263</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+        <v>-116.34338235294109</v>
+      </c>
+      <c r="D25" s="4">
+        <f>STANDARDIZE(B25,F$1,F$2)</f>
+        <v>-1.1863449786176838</v>
+      </c>
+      <c r="E25" s="5">
+        <v>-0.45184879703381298</v>
+      </c>
+      <c r="O25" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="P25" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q25" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>1991</v>
       </c>
       <c r="B26" s="3">
         <v>242.79999999999998</v>
       </c>
-      <c r="C26" s="4">
+      <c r="C26" s="3">
         <f t="shared" si="0"/>
-        <v>-1.2126742670428698</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+        <v>-122.38504901960781</v>
+      </c>
+      <c r="D26" s="4">
+        <f>STANDARDIZE(B26,F$1,F$2)</f>
+        <v>-1.2479514126711346</v>
+      </c>
+      <c r="E26" s="5">
+        <v>0.40128082574528251</v>
+      </c>
+      <c r="O26" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="P26" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="12">
+        <v>0.56509980556847084</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>1990</v>
       </c>
       <c r="B27" s="3">
         <v>316.10833333333335</v>
       </c>
-      <c r="C27" s="4">
+      <c r="C27" s="3">
         <f t="shared" si="0"/>
-        <v>-0.4673295363368441</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+        <v>-49.07671568627444</v>
+      </c>
+      <c r="D27" s="4">
+        <f>STANDARDIZE(B27,F$1,F$2)</f>
+        <v>-0.500431688025336</v>
+      </c>
+      <c r="E27" s="5">
+        <v>1.3183337055627835</v>
+      </c>
+      <c r="O27" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="P27" s="13">
+        <v>0.56509980556847084</v>
+      </c>
+      <c r="Q27" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>1989</v>
       </c>
       <c r="B28" s="3">
         <v>369.30833333333334</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C28" s="3">
         <f t="shared" si="0"/>
-        <v>7.3568583570768231E-2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+        <v>4.1232843137255486</v>
+      </c>
+      <c r="D28" s="4">
+        <f>STANDARDIZE(B28,F$1,F$2)</f>
+        <v>4.2044829212219553E-2</v>
+      </c>
+      <c r="E28" s="5">
+        <v>1.2556397419291438</v>
+      </c>
+      <c r="O28" s="18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>1988</v>
       </c>
       <c r="B29" s="3">
         <v>437.18333333333334</v>
       </c>
-      <c r="C29" s="4">
+      <c r="C29" s="3">
         <f t="shared" si="0"/>
-        <v>0.7636712130581591</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+        <v>71.998284313725549</v>
+      </c>
+      <c r="D29" s="4">
+        <f>STANDARDIZE(B29,F$1,F$2)</f>
+        <v>0.73416125040581148</v>
+      </c>
+      <c r="E29" s="5">
+        <v>0.91961144200152467</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>1987</v>
       </c>
       <c r="B30" s="3">
         <v>312.54166666666669</v>
       </c>
-      <c r="C30" s="4">
+      <c r="C30" s="3">
         <f t="shared" si="0"/>
-        <v>-0.5035927561552116</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+        <v>-52.643382352941103</v>
+      </c>
+      <c r="D30" s="4">
+        <f>STANDARDIZE(B30,F$1,F$2)</f>
+        <v>-0.53680072771482124</v>
+      </c>
+      <c r="E30" s="5">
+        <v>-2.2436243880499956E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>1986</v>
       </c>
       <c r="B31" s="3">
         <v>317.27500000000003</v>
       </c>
-      <c r="C31" s="4">
+      <c r="C31" s="3">
         <f t="shared" si="0"/>
-        <v>-0.45546773546167696</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+        <v>-47.910049019607754</v>
+      </c>
+      <c r="D31" s="4">
+        <f>STANDARDIZE(B31,F$1,F$2)</f>
+        <v>-0.48853527317363499</v>
+      </c>
+      <c r="E31" s="5">
+        <v>0.2128660643177748</v>
+      </c>
+      <c r="O31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>1985</v>
       </c>
       <c r="B32" s="3">
         <v>304.03333333333336</v>
       </c>
-      <c r="C32" s="4">
+      <c r="C32" s="3">
         <f t="shared" si="0"/>
-        <v>-0.59009917539482182</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+        <v>-61.151715686274429</v>
+      </c>
+      <c r="D32" s="4">
+        <f>STANDARDIZE(B32,F$1,F$2)</f>
+        <v>-0.62355958174043891</v>
+      </c>
+      <c r="E32" s="5">
+        <v>3.133791886694659E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>1984</v>
       </c>
       <c r="B33" s="3">
         <v>362.58333333333331</v>
       </c>
-      <c r="C33" s="4">
+      <c r="C33" s="3">
         <f t="shared" si="0"/>
-        <v>5.1937742403414307E-3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+        <v>-2.6017156862744741</v>
+      </c>
+      <c r="D33" s="4">
+        <f>STANDARDIZE(B33,F$1,F$2)</f>
+        <v>-2.6529504968655897E-2</v>
+      </c>
+      <c r="E33" s="5">
+        <v>0.33583947248568996</v>
+      </c>
+      <c r="O33" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="P33" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q33" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>1983</v>
       </c>
       <c r="B34" s="3">
         <v>157.01666666666668</v>
       </c>
-      <c r="C34" s="4">
+      <c r="C34" s="3">
         <f t="shared" si="0"/>
-        <v>-2.0848555399640731</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+        <v>-208.16838235294111</v>
+      </c>
+      <c r="D34" s="4">
+        <f>STANDARDIZE(B34,F$1,F$2)</f>
+        <v>-2.1226778018383334</v>
+      </c>
+      <c r="E34" s="5">
+        <v>-0.29665741333436768</v>
+      </c>
+      <c r="O34" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="P34" s="15">
+        <v>1</v>
+      </c>
+      <c r="Q34" s="12">
+        <v>1.0449919725998263E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>1982</v>
       </c>
       <c r="B35" s="3">
         <v>239.70833333333334</v>
       </c>
-      <c r="C35" s="4">
+      <c r="C35" s="3">
         <f t="shared" si="0"/>
-        <v>-1.244108039362062</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36">
-        <v>1981</v>
-      </c>
-      <c r="B36" s="3">
-        <v>256.24583333333334</v>
-      </c>
-      <c r="C36" s="4">
-        <f t="shared" si="0"/>
-        <v>-1.0759670119565707</v>
-      </c>
+        <v>-125.47671568627445</v>
+      </c>
+      <c r="D35" s="4">
+        <f>STANDARDIZE(B35,F$1,F$2)</f>
+        <v>-1.2794769120281415</v>
+      </c>
+      <c r="E35" s="5">
+        <v>0.1377693096040904</v>
+      </c>
+      <c r="O35" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="P35" s="13">
+        <v>1.0449919725998263E-2</v>
+      </c>
+      <c r="Q35" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1"/>
+  </ignoredErrors>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Data_processed/coral_lumn.xlsx
+++ b/Data_processed/coral_lumn.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GDrive\Academicos\Articulos\Pendientes\Varadero growth rates\Data_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE58C54B-DF38-4718-909C-96F2533DEA02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FBF35D7-11DD-4F83-9A94-0B191B8CBB9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00D95527-D75E-4AD9-900B-59FC494863D4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00D95527-D75E-4AD9-900B-59FC494863D4}"/>
   </bookViews>
   <sheets>
     <sheet name="indexed" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="36">
   <si>
     <t>Core</t>
   </si>
@@ -130,10 +130,25 @@
     <t>Coefficients of determination (R²):</t>
   </si>
   <si>
-    <t>centered</t>
+    <t>center</t>
   </si>
   <si>
-    <t>center</t>
+    <t>WF-3yr</t>
+  </si>
+  <si>
+    <t>G/B-3yr</t>
+  </si>
+  <si>
+    <t>G/B-5yr</t>
+  </si>
+  <si>
+    <t>WF-stda</t>
+  </si>
+  <si>
+    <t>WF-centered</t>
+  </si>
+  <si>
+    <t>G/B-stda</t>
   </si>
 </sst>
 </file>
@@ -216,7 +231,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -225,24 +240,22 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -2366,111 +2379,111 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>columns!$P$2:$P$35</c:f>
+              <c:f>waterflow!$E$2:$E$35</c:f>
               <c:numCache>
-                <c:formatCode>0.000</c:formatCode>
+                <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="34"/>
                 <c:pt idx="0">
-                  <c:v>-3.5011831280982286E-2</c:v>
+                  <c:v>-2.0659110372486018</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-4.5220164614313885E-2</c:v>
+                  <c:v>-2.6682648054931648</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-4.3886831280980698E-2</c:v>
+                  <c:v>-2.5895900275999928</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-2.8407664614313988E-2</c:v>
+                  <c:v>-1.676225027996344</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-1.5990997947648911E-2</c:v>
+                  <c:v>-0.94356615886619133</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-1.7324331280981209E-2</c:v>
+                  <c:v>-1.022240936759311</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-2.5553497947647941E-2</c:v>
+                  <c:v>-1.5078118315687905</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-1.4407664614316085E-2</c:v>
+                  <c:v>-0.85013986011806908</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-9.5951646143168645E-3</c:v>
+                  <c:v>-0.56617308365991559</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-7.6784979476478554E-3</c:v>
+                  <c:v>-0.45307809043832992</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-1.407433128098301E-2</c:v>
+                  <c:v>-0.83047116564478918</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-1.0657664614317719E-2</c:v>
+                  <c:v>-0.62886704729359444</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-1.1574331280984396E-2</c:v>
+                  <c:v>-0.68295595709515688</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-1.4574331280982733E-2</c:v>
+                  <c:v>-0.85997420735471564</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-2.0490997947651191E-2</c:v>
+                  <c:v>-1.2090935342558111</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-1.2053497947650094E-2</c:v>
+                  <c:v>-0.7112297054004616</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.0134002052347268E-2</c:v>
+                  <c:v>0.59796777047809502</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-1.7928497947647948E-2</c:v>
+                  <c:v>-1.0578904454921629</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-3.2178497947648155E-2</c:v>
+                  <c:v>-1.8987271342255452</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.0550668719014666E-2</c:v>
+                  <c:v>0.62255363856975721</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>8.5298353856837483E-3</c:v>
+                  <c:v>0.50331217832554753</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>3.8423353856831266E-3</c:v>
+                  <c:v>0.22672116229479697</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.4048353856823681E-3</c:v>
+                  <c:v>8.2893833958780999E-2</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-7.6576646143156069E-3</c:v>
+                  <c:v>-0.45184879703381298</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>6.8006687190163007E-3</c:v>
+                  <c:v>0.40128082574528251</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>2.2342335385684864E-2</c:v>
+                  <c:v>1.3183337055627835</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>2.1279835385684676E-2</c:v>
+                  <c:v>1.2556397419291438</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1.5585027656514594E-2</c:v>
+                  <c:v>0.91961144200152467</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>-3.8023611431459159E-4</c:v>
+                  <c:v>-2.2436243880499956E-2</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>3.6075274273505986E-3</c:v>
+                  <c:v>0.2128660643177748</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>5.3109640651705092E-4</c:v>
+                  <c:v>3.133791886694659E-2</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>5.6916075940147692E-3</c:v>
+                  <c:v>0.33583947248568996</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>-5.02757336431503E-3</c:v>
+                  <c:v>-0.29665741333436768</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>2.3348323023530959E-3</c:v>
+                  <c:v>0.1377693096040904</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2479,6 +2492,552 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000005-98CB-4519-A278-1D0CF063AAF3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>waterflow!$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>G/B-3yr</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>waterflow!$A$2:$A$35</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="34"/>
+                <c:pt idx="0">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1999</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1998</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1997</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1996</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1995</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1994</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1993</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1992</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1991</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1990</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1989</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1988</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1987</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1986</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1985</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1984</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1983</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1982</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>waterflow!$G$2:$G$35</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="34"/>
+                <c:pt idx="0">
+                  <c:v>-2.3670879213708833</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-2.44125529011392</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-2.3113599536965004</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-1.7364604048208425</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-1.2140107078739488</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-1.157872975731431</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-1.1267308761487236</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-0.97470825844892506</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-0.62313034473877149</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-0.61657411324767819</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-0.63747210112557118</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-0.71409805667784687</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-0.72393240391448899</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-0.91734123290189462</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-0.92676581567032945</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-0.44078515639272592</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-0.39038412680484313</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-0.78621660307987096</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-0.77802131371598371</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-0.25762043911008015</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.4508623263967006</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.2709757248597085</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-4.7411266926745001E-2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1.0775287556750187E-2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.42258857809141764</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.99175142441240327</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1.1645282964978174</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.71760498001672268</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.37001375414626653</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>7.3922579768073815E-2</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.1933478185568038</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2.3506659339422958E-2</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>5.8983789585137558E-2</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>-7.9444051865138643E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C696-48CE-A44B-260A5FDA7F54}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>waterflow!$H$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>G/B-5yr</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>waterflow!$A$2:$A$35</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="34"/>
+                <c:pt idx="0">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1999</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1998</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1997</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1996</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1995</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1994</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1993</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1992</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1991</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1990</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1989</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1988</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1987</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1986</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1985</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1984</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1983</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1982</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>waterflow!$H$2:$H$35</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="34"/>
+                <c:pt idx="0">
+                  <c:v>-2.44125529011392</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-2.2499977245845257</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-1.9887114114408591</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-1.7799773913430006</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-1.5478867965581258</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-1.199996763061741</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-0.97798637419445544</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-0.87988876050888332</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-0.84153480628597888</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-0.66574584943093962</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-0.63230906882635707</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-0.69106929356531721</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-0.84227238232881363</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-0.818424090279948</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-0.57305712672561016</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-0.64804402440501119</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-0.85579460977917721</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-0.48946517521406357</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-0.24655679846886161</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-0.32080612010552134</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-9.2649264215332483E-2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.19672640322301396</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.152471840658119</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.31547614610556618</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.52125986203243557</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.68860338364098439</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.77448589427164682</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.73680294198614538</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.47940378464697792</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.29544373075828723</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>5.2189959691108734E-2</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>8.4231070388026824E-2</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>5.2072321905589816E-2</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>5.8983789585137558E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-C696-48CE-A44B-260A5FDA7F54}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3919,245 +4478,235 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
+            <c:symbol val="none"/>
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>waterflow!$C$2:$C$36</c:f>
+              <c:f>waterflow!$A$2:$A$36</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="35"/>
                 <c:pt idx="0">
-                  <c:v>-105.44338235294111</c:v>
+                  <c:v>2015</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-38.876715686274451</c:v>
+                  <c:v>2014</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-71.135049019607777</c:v>
+                  <c:v>2013</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-8.7100490196078226</c:v>
+                  <c:v>2012</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>150.70661764705898</c:v>
+                  <c:v>2011</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>100.15661764705874</c:v>
+                  <c:v>2010</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>54.073284313725594</c:v>
+                  <c:v>2009</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>195.31495098039221</c:v>
+                  <c:v>2008</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>147.07328431372554</c:v>
+                  <c:v>2007</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>117.22328431372551</c:v>
+                  <c:v>2006</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>36.614950980392166</c:v>
+                  <c:v>2005</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>5.5982843137255713</c:v>
+                  <c:v>2004</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.79828431372556</c:v>
+                  <c:v>2003</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-3.6267156862744514</c:v>
+                  <c:v>2002</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-80.335049019607823</c:v>
+                  <c:v>2001</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>146.58995098039225</c:v>
+                  <c:v>2000</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>172.64828431372558</c:v>
+                  <c:v>1999</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-6.8433823529411484</c:v>
+                  <c:v>1998</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-150.56838235294114</c:v>
+                  <c:v>1997</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>42.239950980392166</c:v>
+                  <c:v>1996</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>26.339950980392246</c:v>
+                  <c:v>1995</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>19.814950980392155</c:v>
+                  <c:v>1994</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>-41.018382352941103</c:v>
+                  <c:v>1993</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-116.34338235294109</c:v>
+                  <c:v>1992</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-122.38504901960781</c:v>
+                  <c:v>1991</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>-49.07671568627444</c:v>
+                  <c:v>1990</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>4.1232843137255486</c:v>
+                  <c:v>1989</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>71.998284313725549</c:v>
+                  <c:v>1988</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>-52.643382352941103</c:v>
+                  <c:v>1987</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>-47.910049019607754</c:v>
+                  <c:v>1986</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>-61.151715686274429</c:v>
+                  <c:v>1985</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>-2.6017156862744741</c:v>
+                  <c:v>1984</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>-208.16838235294111</c:v>
+                  <c:v>1983</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>-125.47671568627445</c:v>
+                  <c:v>1982</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>columns!$O$2:$O$35</c:f>
+              <c:f>waterflow!$D$2:$D$36</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="35"/>
                 <c:pt idx="0">
-                  <c:v>-2.0659110372486018</c:v>
+                  <c:v>-1.0751984741460796</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-2.6682648054931648</c:v>
+                  <c:v>-0.39642303246475213</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-2.5895900275999928</c:v>
+                  <c:v>-0.72535890311427864</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-1.676225027996344</c:v>
+                  <c:v>-8.8815734156489426E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-0.94356615886619133</c:v>
+                  <c:v>1.5367443809366259</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-1.022240936759311</c:v>
+                  <c:v>1.0212897202907882</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-1.5078118315687905</c:v>
+                  <c:v>0.5513813336486092</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-0.85013986011806908</c:v>
+                  <c:v>1.9916123002305841</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-0.56617308365991559</c:v>
+                  <c:v>1.4996955461127566</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-0.45307809043832992</c:v>
+                  <c:v>1.195317274692812</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-0.83047116564478918</c:v>
+                  <c:v>0.37335998283208582</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-0.62886704729359444</c:v>
+                  <c:v>5.7085296560441492E-2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-0.68295595709515688</c:v>
+                  <c:v>1.833697390061597E-2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-0.85997420735471564</c:v>
+                  <c:v>-3.6981355159792777E-2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-1.2090935342558111</c:v>
+                  <c:v>-0.81917063165911952</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-0.7112297054004616</c:v>
+                  <c:v>1.4947670313884811</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.59796777047809502</c:v>
+                  <c:v>1.7604819545403978</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-1.0578904454921629</c:v>
+                  <c:v>-6.97814703937681E-2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-1.8987271342255452</c:v>
+                  <c:v>-1.5353348057315064</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.62255363856975721</c:v>
+                  <c:v>0.43071769729564319</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.50331217832554753</c:v>
+                  <c:v>0.26858655774532192</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.22672116229479697</c:v>
+                  <c:v>0.20205160896759444</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>8.2893833958780999E-2</c:v>
+                  <c:v>-0.41826145115680269</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-0.45184879703381298</c:v>
+                  <c:v>-1.1863449786176838</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.40128082574528251</c:v>
+                  <c:v>-1.2479514126711346</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.3183337055627835</c:v>
+                  <c:v>-0.500431688025336</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1.2556397419291438</c:v>
+                  <c:v>4.2044829212219553E-2</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.91961144200152467</c:v>
+                  <c:v>0.73416125040581148</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>-2.2436243880499956E-2</c:v>
+                  <c:v>-0.53680072771482124</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.2128660643177748</c:v>
+                  <c:v>-0.48853527317363499</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>3.133791886694659E-2</c:v>
+                  <c:v>-0.62355958174043891</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.33583947248568996</c:v>
+                  <c:v>-2.6529504968655897E-2</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>-0.29665741333436768</c:v>
+                  <c:v>-2.1226778018383334</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.1377693096040904</c:v>
+                  <c:v>-1.2794769120281415</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4165,7 +4714,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-F8CE-47DA-9D17-DF30E0F299D7}"/>
+              <c16:uniqueId val="{00000000-8444-4561-BB73-D22980E5C873}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4180,10 +4729,1564 @@
         <c:axId val="1571430320"/>
         <c:axId val="1571426480"/>
       </c:scatterChart>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>columns!$D$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>VAR2</c:v>
+                </c:pt>
+              </c:strCache>
+              <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>indexed!$B$36:$B$97</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="62"/>
+                <c:pt idx="0">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1999</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1998</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1997</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1996</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1995</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1994</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1993</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1992</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1991</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1990</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1989</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1988</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1987</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1986</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1985</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1984</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1983</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1982</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1981</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1980</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1979</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1978</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1977</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1976</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1975</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1974</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1973</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1972</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1971</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1970</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>1969</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>1968</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>1967</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>1966</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>1965</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>1964</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>1963</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>1962</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1961</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1960</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1959</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1958</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1957</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1956</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1955</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1954</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>indexed!$D$36:$D$97</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="62"/>
+                <c:pt idx="0">
+                  <c:v>1.0408329997330599E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.0278870007599E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.7554244932537402E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.1766349038549199E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.2155784524109899E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.4409509628620503E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.1304431179423301E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.4908864030197002E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.0573309809820499E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.9754933382652001E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3.0698312064938699E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.9344350548119201E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3.0001388856740099E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.82762886624371E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.8690461025168199E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3.00427725388017E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3.0724952844109001E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3.6094467804091597E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.1843798093543899E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2.6288607971722399E-2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2.54481052458932E-2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2.50361859327775E-2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2.1478671591449301E-2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2.2516492272163999E-2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1.6876332719539599E-2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2.4094982502964799E-2</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>4.1861514110652497E-2</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>3.6337121014691803E-2</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1.8118089069080901E-2</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1.72281921878241E-2</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1.9764522853748901E-2</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2.0424843755197701E-2</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2.0630956440174101E-2</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1.8342490825865702E-2</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1.9522131962560699E-2</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1.50400979203775E-2</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>2.3591215622461099E-2</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1.3937903411745599E-2</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1.18203086664306E-2</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>2.3654553024478799E-2</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>3.1677709398365103E-2</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>2.6834368510053101E-2</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>3.2137017266508701E-2</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1.9570192238259201E-2</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1.7399712641305298E-2</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>2.9568103207218501E-2</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>1.99732776023821E-2</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>3.0639645539527301E-2</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>1.8776193824773201E-2</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>3.2872918761174597E-2</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>2.8122567234852298E-2</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>3.4587066246143897E-2</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>2.9005746557076099E-2</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>2.9787123514578E-2</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>2.2584521382145901E-2</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>2.7971170222862701E-2</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>2.1742292260184301E-2</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1.9055540831045301E-2</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>2.4054231656946701E-2</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>2.5282045371801301E-2</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>2.97107265600704E-2</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>3.0797274050546299E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-8444-4561-BB73-D22980E5C873}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1571426960"/>
+        <c:axId val="1571430321"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredScatterSeries>
+              <c15:ser>
+                <c:idx val="1"/>
+                <c:order val="1"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>columns!$A$2</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>VAR1</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="19050" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent2"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="none"/>
+                </c:marker>
+                <c:xVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>columns!$B$2:$B$35</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="34"/>
+                      <c:pt idx="0">
+                        <c:v>2015</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>2014</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>2013</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>2012</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>2011</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>2010</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>2009</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>2008</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>2007</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>2006</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>2005</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>2004</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>2003</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>2002</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>2001</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>2000</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>1999</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>1998</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>1997</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>1996</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>1995</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>1994</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>1993</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>1992</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>1991</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>1990</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>1989</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>1988</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>1987</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>1986</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>1985</c:v>
+                      </c:pt>
+                      <c:pt idx="31">
+                        <c:v>1984</c:v>
+                      </c:pt>
+                      <c:pt idx="32">
+                        <c:v>1983</c:v>
+                      </c:pt>
+                      <c:pt idx="33">
+                        <c:v>1982</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:xVal>
+                <c:yVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>columns!$C$2:$C$35</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0.000</c:formatCode>
+                      <c:ptCount val="34"/>
+                      <c:pt idx="0">
+                        <c:v>0.96499999999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>0.96316666666666595</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>0.96408333333333296</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>0.99783333333333302</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>0.99549999999999905</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>0.99691666666666601</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>0.98608333333333298</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>1.0197499999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>0.99433333333333296</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>0.99208333333333298</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>0.99549999999999905</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>1.0119166666666599</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>1.0165833333333301</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>1.0248333333333299</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>1.00366666666666</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>1.0249999999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>1.03033333333333</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>1.00833333333333</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>0.98308333333333298</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>1.03816666666666</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>1.02633333333333</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>1.01383333333333</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>1.02125</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>0.99616666666666598</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>1.0179166666666599</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>1.02325</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>1.03216666666666</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>1.03705410241666</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>1.0229430473333301</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>1.0263941015</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>1.02783837741666</c:v>
+                      </c:pt>
+                      <c:pt idx="31">
+                        <c:v>1.04564708883333</c:v>
+                      </c:pt>
+                      <c:pt idx="32">
+                        <c:v>1.01718703166666</c:v>
+                      </c:pt>
+                      <c:pt idx="33">
+                        <c:v>1.0290533209999999</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:yVal>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000002-8444-4561-BB73-D22980E5C873}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredScatterSeries>
+            <c15:filteredScatterSeries>
+              <c15:ser>
+                <c:idx val="3"/>
+                <c:order val="3"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>columns!$G$2</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>VAR3</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="19050" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent4"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="none"/>
+                </c:marker>
+                <c:xVal>
+                  <c:numRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>columns!$H$2:$H$36</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="35"/>
+                      <c:pt idx="0">
+                        <c:v>2015</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>2014</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>2013</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>2012</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>2011</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>2010</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>2009</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>2008</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>2007</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>2006</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>2005</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>2004</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>2003</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>2002</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>2001</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>2000</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>1999</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>1998</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>1997</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>1996</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>1995</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>1994</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>1993</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>1992</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>1991</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>1990</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>1989</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>1988</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>1987</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>1986</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>1985</c:v>
+                      </c:pt>
+                      <c:pt idx="31">
+                        <c:v>1984</c:v>
+                      </c:pt>
+                      <c:pt idx="32">
+                        <c:v>1983</c:v>
+                      </c:pt>
+                      <c:pt idx="33">
+                        <c:v>1982</c:v>
+                      </c:pt>
+                      <c:pt idx="34">
+                        <c:v>1981</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:xVal>
+                <c:yVal>
+                  <c:numRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>columns!$I$2:$I$36</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0.000</c:formatCode>
+                      <c:ptCount val="35"/>
+                      <c:pt idx="0">
+                        <c:v>1.00616666666666</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>0.97299999999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>0.97808333333333297</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>0.99783333333333302</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>1.0342499999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>1.02475</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>1.0268333333333299</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>1.01508333333333</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>1.0256666666666601</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>1.05725</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>1.0260833333333299</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>1.0253333333333301</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>1.00091666666666</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>1.0004166666666601</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>1.00366666666666</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>1.0064166666666601</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>1.03091666666666</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>0.99708333333333299</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>1.00183333333333</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>1.0585833333333301</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>1.06375</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>1.08083333333333</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>1.04341666666666</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>1.0356666666666601</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>1.0471666666666599</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>1.0689166666666601</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>1.077</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>1.0564166666666599</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>1.0345</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>1.05591666666666</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>1.046</c:v>
+                      </c:pt>
+                      <c:pt idx="31">
+                        <c:v>1.0356666666666601</c:v>
+                      </c:pt>
+                      <c:pt idx="32">
+                        <c:v>1.0137499999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="33">
+                        <c:v>1.0347500000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="34">
+                        <c:v>1.0753333333333299</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:yVal>
+                <c:smooth val="0"/>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000004-8444-4561-BB73-D22980E5C873}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredScatterSeries>
+            <c15:filteredScatterSeries>
+              <c15:ser>
+                <c:idx val="4"/>
+                <c:order val="4"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>columns!$J$2</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>VAR4</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="19050" cap="rnd">
+                    <a:solidFill>
+                      <a:srgbClr val="C00000"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="none"/>
+                </c:marker>
+                <c:xVal>
+                  <c:numRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>columns!$K$2:$K$36</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="35"/>
+                      <c:pt idx="0">
+                        <c:v>2015</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>2014</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>2013</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>2012</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>2011</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>2010</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>2009</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>2008</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>2007</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>2006</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>2005</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>2004</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>2003</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>2002</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>2001</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>2000</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>1999</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>1998</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>1997</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>1996</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>1995</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>1994</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>1993</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>1992</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>1991</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>1990</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>1989</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>1988</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>1987</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>1986</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>1985</c:v>
+                      </c:pt>
+                      <c:pt idx="31">
+                        <c:v>1984</c:v>
+                      </c:pt>
+                      <c:pt idx="32">
+                        <c:v>1983</c:v>
+                      </c:pt>
+                      <c:pt idx="33">
+                        <c:v>1982</c:v>
+                      </c:pt>
+                      <c:pt idx="34">
+                        <c:v>1981</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:xVal>
+                <c:yVal>
+                  <c:numRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>columns!$L$2:$L$36</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0.000</c:formatCode>
+                      <c:ptCount val="35"/>
+                      <c:pt idx="0">
+                        <c:v>0.98266666666666602</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>0.97558333333333302</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>0.98016666666666596</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>0.99666666666666603</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>1.00616666666666</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>1.00183333333333</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>0.99158333333333304</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>1.00016666666666</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>1.02466666666666</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>1.02558333333333</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>1.03141666666666</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>1.02016666666666</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>1.0291666666666599</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>1.0177499999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>1.0240833333333299</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>1.0216666666666601</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>1.0500833333333299</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>1.024</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>0.99774999999999903</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>1.0234999999999901</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>1.0199166666666599</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>1.0046666666666599</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>1.0113333333333301</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>1.0169999999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>1.0337499999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>1.0555000000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>1.04575</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>1.04216666666666</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>1.0125</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>1.00708333333333</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>1.0028333333333299</c:v>
+                      </c:pt>
+                      <c:pt idx="31">
+                        <c:v>1.0045833333333301</c:v>
+                      </c:pt>
+                      <c:pt idx="32">
+                        <c:v>1.022</c:v>
+                      </c:pt>
+                      <c:pt idx="33">
+                        <c:v>1.0235000000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="34">
+                        <c:v>1.04508333333333</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:yVal>
+                <c:smooth val="0"/>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000005-8444-4561-BB73-D22980E5C873}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredScatterSeries>
+            <c15:filteredScatterSeries>
+              <c15:ser>
+                <c:idx val="5"/>
+                <c:order val="5"/>
+                <c:tx>
+                  <c:v>G/B STDA</c:v>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="19050" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent6"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent6"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent6"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:xVal>
+                  <c:numRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>columns!$K$2:$K$35</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="34"/>
+                      <c:pt idx="0">
+                        <c:v>2015</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>2014</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>2013</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>2012</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>2011</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>2010</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>2009</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>2008</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>2007</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>2006</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>2005</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>2004</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>2003</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>2002</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>2001</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>2000</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>1999</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>1998</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>1997</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>1996</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>1995</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>1994</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>1993</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>1992</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>1991</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>1990</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>1989</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>1988</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>1987</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>1986</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>1985</c:v>
+                      </c:pt>
+                      <c:pt idx="31">
+                        <c:v>1984</c:v>
+                      </c:pt>
+                      <c:pt idx="32">
+                        <c:v>1983</c:v>
+                      </c:pt>
+                      <c:pt idx="33">
+                        <c:v>1982</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:xVal>
+                <c:yVal>
+                  <c:numRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>columns!$O$2:$O$35</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0.0</c:formatCode>
+                      <c:ptCount val="34"/>
+                      <c:pt idx="0">
+                        <c:v>-2.0659110372486018</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>-2.6682648054931648</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>-2.5895900275999928</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>-1.676225027996344</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>-0.94356615886619133</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>-1.022240936759311</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>-1.5078118315687905</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>-0.85013986011806908</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>-0.56617308365991559</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>-0.45307809043832992</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>-0.83047116564478918</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>-0.62886704729359444</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>-0.68295595709515688</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>-0.85997420735471564</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>-1.2090935342558111</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>-0.7112297054004616</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>0.59796777047809502</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>-1.0578904454921629</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>-1.8987271342255452</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>0.62255363856975721</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>0.50331217832554753</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>0.22672116229479697</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>8.2893833958780999E-2</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>-0.45184879703381298</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>0.40128082574528251</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>1.3183337055627835</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>1.2556397419291438</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>0.91961144200152467</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>-2.2436243880499956E-2</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>0.2128660643177748</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>3.133791886694659E-2</c:v>
+                      </c:pt>
+                      <c:pt idx="31">
+                        <c:v>0.33583947248568996</c:v>
+                      </c:pt>
+                      <c:pt idx="32">
+                        <c:v>-0.29665741333436768</c:v>
+                      </c:pt>
+                      <c:pt idx="33">
+                        <c:v>0.1377693096040904</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:yVal>
+                <c:smooth val="0"/>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000001-8444-4561-BB73-D22980E5C873}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredScatterSeries>
+          </c:ext>
+        </c:extLst>
+      </c:scatterChart>
       <c:valAx>
         <c:axId val="1571430320"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="2015"/>
+          <c:min val="1980"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -4201,7 +6304,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -4248,7 +6351,7 @@
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
-        <c:axPos val="r"/>
+        <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
@@ -4301,7 +6404,70 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="1571430320"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1571430321"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:numFmt formatCode="0.00" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1571426960"/>
         <c:crosses val="max"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1571426960"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1571430321"/>
+        <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:spPr>
@@ -4312,6 +6478,34 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -4381,11 +6575,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>waterflow!$B$1</c:f>
+              <c:f>waterflow!$F$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>WaterFlow</c:v>
+                  <c:v>WF-3yr</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4515,111 +6709,111 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>waterflow!$D$2:$D$36</c:f>
+              <c:f>waterflow!$F$2:$F$35</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="35"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
-                  <c:v>-1.0751984741460796</c:v>
+                  <c:v>-0.7358107533054159</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-0.39642303246475213</c:v>
+                  <c:v>-0.73232680324170352</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-0.72535890311427864</c:v>
+                  <c:v>-0.40353255657850678</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-8.8815734156489426E-2</c:v>
+                  <c:v>0.24085658122195261</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.5367443809366259</c:v>
+                  <c:v>0.82307278902364145</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.0212897202907882</c:v>
+                  <c:v>1.0364718116253411</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.5513813336486092</c:v>
+                  <c:v>1.188094451389994</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.9916123002305841</c:v>
+                  <c:v>1.3475630599973165</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.4996955461127566</c:v>
+                  <c:v>1.5622083736787176</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.195317274692812</c:v>
+                  <c:v>1.0227909345458848</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.37335998283208582</c:v>
+                  <c:v>0.54192085136177981</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>5.7085296560441492E-2</c:v>
+                  <c:v>0.14959408443104774</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.833697390061597E-2</c:v>
+                  <c:v>1.2813638433754894E-2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-3.6981355159792777E-2</c:v>
+                  <c:v>-0.27927167097276545</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-0.81917063165911952</c:v>
+                  <c:v>0.21287168152318961</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.4947670313884811</c:v>
+                  <c:v>0.81202611808991987</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.7604819545403978</c:v>
+                  <c:v>1.0618225051783703</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-6.97814703937681E-2</c:v>
+                  <c:v>5.1788559471707796E-2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-1.5353348057315064</c:v>
+                  <c:v>-0.39146619294321039</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.43071769729564319</c:v>
+                  <c:v>-0.27867685023018041</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.26858655774532192</c:v>
+                  <c:v>0.30045195466951985</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.20205160896759444</c:v>
+                  <c:v>1.7458905185371226E-2</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>-0.41826145115680269</c:v>
+                  <c:v>-0.46751827360229736</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-1.1863449786176838</c:v>
+                  <c:v>-0.95085261414854039</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-1.2479514126711346</c:v>
+                  <c:v>-0.97824269310471823</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>-0.500431688025336</c:v>
+                  <c:v>-0.56877942382808377</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>4.2044829212219553E-2</c:v>
+                  <c:v>9.1924797197565009E-2</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.73416125040581148</c:v>
+                  <c:v>7.9801783967736586E-2</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>-0.53680072771482124</c:v>
+                  <c:v>-9.7058250160881585E-2</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>-0.48853527317363499</c:v>
+                  <c:v>-0.54963186087629834</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>-0.62355958174043891</c:v>
+                  <c:v>-0.37954145329424321</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>-2.6529504968655897E-2</c:v>
+                  <c:v>-0.92425562951580942</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>-2.1226778018383334</c:v>
+                  <c:v>-1.1428947396117104</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>-1.2794769120281415</c:v>
+                  <c:v>-1.7010773569332374</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4627,7 +6821,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-8444-4561-BB73-D22980E5C873}"/>
+              <c16:uniqueId val="{00000000-0EB5-41F2-9927-41B5BDB47A4B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4646,38 +6840,55 @@
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
+          <c:idx val="6"/>
+          <c:order val="6"/>
           <c:tx>
             <c:strRef>
-              <c:f>columns!$D$2</c:f>
+              <c:f>waterflow!$G$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>VAR2</c:v>
+                  <c:v>G/B-3yr</c:v>
                 </c:pt>
               </c:strCache>
-              <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="25400" cap="rnd">
+            <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:srgbClr val="FFC000"/>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="none"/>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>indexed!$B$36:$B$97</c:f>
+              <c:f>waterflow!$A$2:$A$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>2015</c:v>
                 </c:pt>
@@ -4779,285 +6990,117 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>1982</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>1981</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>1980</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>1979</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>1978</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>1977</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>1976</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>1975</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>1974</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>1973</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>1972</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>1971</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>1970</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>1969</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>1968</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>1967</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>1966</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>1965</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>1964</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>1963</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>1962</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>1961</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>1960</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>1959</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>1958</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>1957</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>1956</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>1955</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>1954</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>indexed!$D$36:$D$97</c:f>
+              <c:f>waterflow!$G$2:$G$35</c:f>
               <c:numCache>
-                <c:formatCode>0.000</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
-                  <c:v>1.0408329997330599E-2</c:v>
+                  <c:v>-2.3670879213708833</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8.0278870007599E-3</c:v>
+                  <c:v>-2.44125529011392</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.7554244932537402E-2</c:v>
+                  <c:v>-2.3113599536965004</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.1766349038549199E-2</c:v>
+                  <c:v>-1.7364604048208425</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.2155784524109899E-2</c:v>
+                  <c:v>-1.2140107078739488</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.4409509628620503E-2</c:v>
+                  <c:v>-1.157872975731431</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.1304431179423301E-2</c:v>
+                  <c:v>-1.1267308761487236</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.4908864030197002E-2</c:v>
+                  <c:v>-0.97470825844892506</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.0573309809820499E-2</c:v>
+                  <c:v>-0.62313034473877149</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.9754933382652001E-2</c:v>
+                  <c:v>-0.61657411324767819</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3.0698312064938699E-2</c:v>
+                  <c:v>-0.63747210112557118</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.9344350548119201E-2</c:v>
+                  <c:v>-0.71409805667784687</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3.0001388856740099E-2</c:v>
+                  <c:v>-0.72393240391448899</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.82762886624371E-2</c:v>
+                  <c:v>-0.91734123290189462</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.8690461025168199E-2</c:v>
+                  <c:v>-0.92676581567032945</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>3.00427725388017E-2</c:v>
+                  <c:v>-0.44078515639272592</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>3.0724952844109001E-2</c:v>
+                  <c:v>-0.39038412680484313</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>3.6094467804091597E-2</c:v>
+                  <c:v>-0.78621660307987096</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2.1843798093543899E-2</c:v>
+                  <c:v>-0.77802131371598371</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2.6288607971722399E-2</c:v>
+                  <c:v>-0.25762043911008015</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2.54481052458932E-2</c:v>
+                  <c:v>0.4508623263967006</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>2.50361859327775E-2</c:v>
+                  <c:v>0.2709757248597085</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>2.1478671591449301E-2</c:v>
+                  <c:v>-4.7411266926745001E-2</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>2.2516492272163999E-2</c:v>
+                  <c:v>1.0775287556750187E-2</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1.6876332719539599E-2</c:v>
+                  <c:v>0.42258857809141764</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>2.4094982502964799E-2</c:v>
+                  <c:v>0.99175142441240327</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>4.1861514110652497E-2</c:v>
+                  <c:v>1.1645282964978174</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>3.6337121014691803E-2</c:v>
+                  <c:v>0.71760498001672268</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1.8118089069080901E-2</c:v>
+                  <c:v>0.37001375414626653</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>1.72281921878241E-2</c:v>
+                  <c:v>7.3922579768073815E-2</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>1.9764522853748901E-2</c:v>
+                  <c:v>0.1933478185568038</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>2.0424843755197701E-2</c:v>
+                  <c:v>2.3506659339422958E-2</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>2.0630956440174101E-2</c:v>
+                  <c:v>5.8983789585137558E-2</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>1.8342490825865702E-2</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>1.9522131962560699E-2</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>1.50400979203775E-2</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>2.3591215622461099E-2</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>1.3937903411745599E-2</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>1.18203086664306E-2</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>2.3654553024478799E-2</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>3.1677709398365103E-2</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>2.6834368510053101E-2</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>3.2137017266508701E-2</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>1.9570192238259201E-2</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>1.7399712641305298E-2</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>2.9568103207218501E-2</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>1.99732776023821E-2</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>3.0639645539527301E-2</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>1.8776193824773201E-2</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>3.2872918761174597E-2</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>2.8122567234852298E-2</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>3.4587066246143897E-2</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>2.9005746557076099E-2</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>2.9787123514578E-2</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>2.2584521382145901E-2</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>2.7971170222862701E-2</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>2.1742292260184301E-2</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>1.9055540831045301E-2</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>2.4054231656946701E-2</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>2.5282045371801301E-2</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>2.97107265600704E-2</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>3.0797274050546299E-2</c:v>
+                  <c:v>-7.9444051865138643E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5065,7 +7108,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-8444-4561-BB73-D22980E5C873}"/>
+              <c16:uniqueId val="{00000002-0EB5-41F2-9927-41B5BDB47A4B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5351,7 +7394,288 @@
                 <c:smooth val="0"/>
                 <c:extLst>
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                    <c16:uniqueId val="{00000002-8444-4561-BB73-D22980E5C873}"/>
+                    <c16:uniqueId val="{00000004-0EB5-41F2-9927-41B5BDB47A4B}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredScatterSeries>
+            <c15:filteredScatterSeries>
+              <c15:ser>
+                <c:idx val="2"/>
+                <c:order val="2"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>columns!$D$2</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>VAR2</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="19050" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent3"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="none"/>
+                </c:marker>
+                <c:xVal>
+                  <c:numRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>columns!$E$2:$E$36</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="35"/>
+                      <c:pt idx="0">
+                        <c:v>2015</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>2014</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>2013</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>2012</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>2011</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>2010</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>2009</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>2008</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>2007</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>2006</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>2005</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>2004</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>2003</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>2002</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>2001</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>2000</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>1999</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>1998</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>1997</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>1996</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>1995</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>1994</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>1993</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>1992</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>1991</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>1990</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>1989</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>1988</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>1987</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>1986</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>1985</c:v>
+                      </c:pt>
+                      <c:pt idx="31">
+                        <c:v>1984</c:v>
+                      </c:pt>
+                      <c:pt idx="32">
+                        <c:v>1983</c:v>
+                      </c:pt>
+                      <c:pt idx="33">
+                        <c:v>1982</c:v>
+                      </c:pt>
+                      <c:pt idx="34">
+                        <c:v>1981</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:xVal>
+                <c:yVal>
+                  <c:numRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>columns!$F$2:$F$36</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0.000</c:formatCode>
+                      <c:ptCount val="35"/>
+                      <c:pt idx="0">
+                        <c:v>0.97716666666666596</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>0.97841666666666605</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>0.97316666666666596</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>0.96508333333333296</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>0.97116666666666596</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>0.97824999999999995</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>0.96433333333333304</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>0.97841666666666605</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>0.98799999999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>0.96541666666666603</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>0.96174999999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>0.97099999999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>0.97808333333333297</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>0.96975</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>0.957666666666666</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>0.96975</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>1.0002499999999901</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>0.96991666666666598</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>0.959666666666666</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>0.99299999999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>0.99516666666666598</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>0.98708333333333298</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>1.0006666666666599</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>0.99158333333333304</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>0.99941666666666595</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>1.01275</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>1.00125</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>0.99774999999999903</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>0.99958333333333305</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>0.99608333333333299</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>0.99649999999999905</c:v>
+                      </c:pt>
+                      <c:pt idx="31">
+                        <c:v>1.0079166666666599</c:v>
+                      </c:pt>
+                      <c:pt idx="32">
+                        <c:v>0.998</c:v>
+                      </c:pt>
+                      <c:pt idx="33">
+                        <c:v>0.99308333333333298</c:v>
+                      </c:pt>
+                      <c:pt idx="34">
+                        <c:v>1.00925</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:yVal>
+                <c:smooth val="0"/>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000005-0EB5-41F2-9927-41B5BDB47A4B}"/>
                   </c:ext>
                 </c:extLst>
               </c15:ser>
@@ -5632,7 +7956,7 @@
                 <c:smooth val="0"/>
                 <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                    <c16:uniqueId val="{00000004-8444-4561-BB73-D22980E5C873}"/>
+                    <c16:uniqueId val="{00000006-0EB5-41F2-9927-41B5BDB47A4B}"/>
                   </c:ext>
                 </c:extLst>
               </c15:ser>
@@ -5913,7 +8237,7 @@
                 <c:smooth val="0"/>
                 <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                    <c16:uniqueId val="{00000005-8444-4561-BB73-D22980E5C873}"/>
+                    <c16:uniqueId val="{00000007-0EB5-41F2-9927-41B5BDB47A4B}"/>
                   </c:ext>
                 </c:extLst>
               </c15:ser>
@@ -6071,7 +8395,7 @@
                     <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>columns!$O$2:$O$35</c15:sqref>
+                          <c15:sqref>waterflow!$E$2:$E$35</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -6186,7 +8510,300 @@
                 <c:smooth val="0"/>
                 <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                    <c16:uniqueId val="{00000001-8444-4561-BB73-D22980E5C873}"/>
+                    <c16:uniqueId val="{00000001-0EB5-41F2-9927-41B5BDB47A4B}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredScatterSeries>
+            <c15:filteredScatterSeries>
+              <c15:ser>
+                <c:idx val="7"/>
+                <c:order val="7"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>waterflow!$H$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>G/B-5yr</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="19050" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent2">
+                        <a:lumMod val="60000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent2">
+                        <a:lumMod val="60000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent2">
+                          <a:lumMod val="60000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:xVal>
+                  <c:numRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>waterflow!$A$2:$A$35</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="34"/>
+                      <c:pt idx="0">
+                        <c:v>2015</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>2014</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>2013</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>2012</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>2011</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>2010</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>2009</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>2008</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>2007</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>2006</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>2005</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>2004</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>2003</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>2002</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>2001</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>2000</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>1999</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>1998</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>1997</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>1996</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>1995</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>1994</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>1993</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>1992</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>1991</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>1990</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>1989</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>1988</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>1987</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>1986</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>1985</c:v>
+                      </c:pt>
+                      <c:pt idx="31">
+                        <c:v>1984</c:v>
+                      </c:pt>
+                      <c:pt idx="32">
+                        <c:v>1983</c:v>
+                      </c:pt>
+                      <c:pt idx="33">
+                        <c:v>1982</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:xVal>
+                <c:yVal>
+                  <c:numRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>waterflow!$H$2:$H$35</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0.0</c:formatCode>
+                      <c:ptCount val="34"/>
+                      <c:pt idx="0">
+                        <c:v>-2.44125529011392</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>-2.2499977245845257</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>-1.9887114114408591</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>-1.7799773913430006</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>-1.5478867965581258</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>-1.199996763061741</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>-0.97798637419445544</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>-0.87988876050888332</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>-0.84153480628597888</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>-0.66574584943093962</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>-0.63230906882635707</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>-0.69106929356531721</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>-0.84227238232881363</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>-0.818424090279948</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>-0.57305712672561016</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>-0.64804402440501119</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>-0.85579460977917721</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>-0.48946517521406357</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>-0.24655679846886161</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>-0.32080612010552134</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>-9.2649264215332483E-2</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>0.19672640322301396</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>0.152471840658119</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>0.31547614610556618</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>0.52125986203243557</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>0.68860338364098439</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>0.77448589427164682</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>0.73680294198614538</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>0.47940378464697792</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>0.29544373075828723</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>5.2189959691108734E-2</c:v>
+                      </c:pt>
+                      <c:pt idx="31">
+                        <c:v>8.4231070388026824E-2</c:v>
+                      </c:pt>
+                      <c:pt idx="32">
+                        <c:v>5.2072321905589816E-2</c:v>
+                      </c:pt>
+                      <c:pt idx="33">
+                        <c:v>5.8983789585137558E-2</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:yVal>
+                <c:smooth val="0"/>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000003-0EB5-41F2-9927-41B5BDB47A4B}"/>
                   </c:ext>
                 </c:extLst>
               </c15:ser>
@@ -8691,13 +11308,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>295275</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>148590</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>104775</xdr:colOff>
       <xdr:row>15</xdr:row>
       <xdr:rowOff>148590</xdr:rowOff>
@@ -8727,13 +11344,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>295275</xdr:colOff>
       <xdr:row>16</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
       <xdr:row>31</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
@@ -8765,23 +11382,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>249555</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>68580</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>120015</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="6" name="Gráfico 5">
+        <xdr:cNvPr id="7" name="Gráfico 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{739F7A7E-BF48-4392-BC72-2DB1FAFC4CC3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C5FA71F-E5C0-4C1B-AE32-2A903A84EE0E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8803,23 +11420,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>594360</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>413385</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="7" name="Gráfico 6">
+        <xdr:cNvPr id="2" name="Gráfico 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C5FA71F-E5C0-4C1B-AE32-2A903A84EE0E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE3A77FB-C8F2-41EA-B128-5F79A68AAF1B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12396,7 +15013,7 @@
         <v>10</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q1" s="3">
         <f>AVERAGE(N2:N66)</f>
@@ -12445,7 +15062,7 @@
         <v>0.9827499999999979</v>
       </c>
       <c r="O2" s="4">
-        <f>STANDARDIZE(N2,Q$1,Q$2)</f>
+        <f t="shared" ref="O2:O35" si="0">STANDARDIZE(N2,Q$1,Q$2)</f>
         <v>-2.0659110372486018</v>
       </c>
       <c r="P2" s="2">
@@ -12495,15 +15112,15 @@
         <v>0.97558333333333302</v>
       </c>
       <c r="N3" s="2">
-        <f t="shared" ref="N3:N66" si="0">AVERAGE(L3,I3,F3,C3)</f>
+        <f t="shared" ref="N3:N66" si="1">AVERAGE(L3,I3,F3,C3)</f>
         <v>0.9725416666666663</v>
       </c>
       <c r="O3" s="4">
-        <f>STANDARDIZE(N3,Q$1,Q$2)</f>
+        <f t="shared" si="0"/>
         <v>-2.6682648054931648</v>
       </c>
       <c r="P3" s="2">
-        <f t="shared" ref="P3:P66" si="1">N3-Q$1</f>
+        <f t="shared" ref="P3:P66" si="2">N3-Q$1</f>
         <v>-4.5220164614313885E-2</v>
       </c>
     </row>
@@ -12545,15 +15162,15 @@
         <v>0.98016666666666596</v>
       </c>
       <c r="N4" s="2">
+        <f t="shared" si="1"/>
+        <v>0.97387499999999949</v>
+      </c>
+      <c r="O4" s="4">
         <f t="shared" si="0"/>
-        <v>0.97387499999999949</v>
-      </c>
-      <c r="O4" s="4">
-        <f>STANDARDIZE(N4,Q$1,Q$2)</f>
         <v>-2.5895900275999928</v>
       </c>
       <c r="P4" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-4.3886831280980698E-2</v>
       </c>
     </row>
@@ -12595,15 +15212,15 @@
         <v>0.99666666666666603</v>
       </c>
       <c r="N5" s="2">
+        <f t="shared" si="1"/>
+        <v>0.9893541666666662</v>
+      </c>
+      <c r="O5" s="4">
         <f t="shared" si="0"/>
-        <v>0.9893541666666662</v>
-      </c>
-      <c r="O5" s="4">
-        <f>STANDARDIZE(N5,Q$1,Q$2)</f>
         <v>-1.676225027996344</v>
       </c>
       <c r="P5" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-2.8407664614313988E-2</v>
       </c>
     </row>
@@ -12645,15 +15262,15 @@
         <v>1.00616666666666</v>
       </c>
       <c r="N6" s="2">
+        <f t="shared" si="1"/>
+        <v>1.0017708333333313</v>
+      </c>
+      <c r="O6" s="4">
         <f t="shared" si="0"/>
-        <v>1.0017708333333313</v>
-      </c>
-      <c r="O6" s="4">
-        <f>STANDARDIZE(N6,Q$1,Q$2)</f>
         <v>-0.94356615886619133</v>
       </c>
       <c r="P6" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-1.5990997947648911E-2</v>
       </c>
     </row>
@@ -12695,15 +15312,15 @@
         <v>1.00183333333333</v>
       </c>
       <c r="N7" s="2">
+        <f t="shared" si="1"/>
+        <v>1.000437499999999</v>
+      </c>
+      <c r="O7" s="4">
         <f t="shared" si="0"/>
-        <v>1.000437499999999</v>
-      </c>
-      <c r="O7" s="4">
-        <f>STANDARDIZE(N7,Q$1,Q$2)</f>
         <v>-1.022240936759311</v>
       </c>
       <c r="P7" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-1.7324331280981209E-2</v>
       </c>
     </row>
@@ -12745,15 +15362,15 @@
         <v>0.99158333333333304</v>
       </c>
       <c r="N8" s="2">
+        <f t="shared" si="1"/>
+        <v>0.99220833333333225</v>
+      </c>
+      <c r="O8" s="4">
         <f t="shared" si="0"/>
-        <v>0.99220833333333225</v>
-      </c>
-      <c r="O8" s="4">
-        <f>STANDARDIZE(N8,Q$1,Q$2)</f>
         <v>-1.5078118315687905</v>
       </c>
       <c r="P8" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-2.5553497947647941E-2</v>
       </c>
     </row>
@@ -12795,15 +15412,15 @@
         <v>1.00016666666666</v>
       </c>
       <c r="N9" s="2">
+        <f t="shared" si="1"/>
+        <v>1.0033541666666641</v>
+      </c>
+      <c r="O9" s="4">
         <f t="shared" si="0"/>
-        <v>1.0033541666666641</v>
-      </c>
-      <c r="O9" s="4">
-        <f>STANDARDIZE(N9,Q$1,Q$2)</f>
         <v>-0.85013986011806908</v>
       </c>
       <c r="P9" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-1.4407664614316085E-2</v>
       </c>
     </row>
@@ -12845,15 +15462,15 @@
         <v>1.02466666666666</v>
       </c>
       <c r="N10" s="2">
+        <f t="shared" si="1"/>
+        <v>1.0081666666666633</v>
+      </c>
+      <c r="O10" s="4">
         <f t="shared" si="0"/>
-        <v>1.0081666666666633</v>
-      </c>
-      <c r="O10" s="4">
-        <f>STANDARDIZE(N10,Q$1,Q$2)</f>
         <v>-0.56617308365991559</v>
       </c>
       <c r="P10" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-9.5951646143168645E-3</v>
       </c>
     </row>
@@ -12895,15 +15512,15 @@
         <v>1.02558333333333</v>
       </c>
       <c r="N11" s="2">
+        <f t="shared" si="1"/>
+        <v>1.0100833333333323</v>
+      </c>
+      <c r="O11" s="4">
         <f t="shared" si="0"/>
-        <v>1.0100833333333323</v>
-      </c>
-      <c r="O11" s="4">
-        <f>STANDARDIZE(N11,Q$1,Q$2)</f>
         <v>-0.45307809043832992</v>
       </c>
       <c r="P11" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-7.6784979476478554E-3</v>
       </c>
     </row>
@@ -12945,15 +15562,15 @@
         <v>1.03141666666666</v>
       </c>
       <c r="N12" s="2">
+        <f t="shared" si="1"/>
+        <v>1.0036874999999972</v>
+      </c>
+      <c r="O12" s="4">
         <f t="shared" si="0"/>
-        <v>1.0036874999999972</v>
-      </c>
-      <c r="O12" s="4">
-        <f>STANDARDIZE(N12,Q$1,Q$2)</f>
         <v>-0.83047116564478918</v>
       </c>
       <c r="P12" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-1.407433128098301E-2</v>
       </c>
     </row>
@@ -12995,15 +15612,15 @@
         <v>1.02016666666666</v>
       </c>
       <c r="N13" s="2">
+        <f t="shared" si="1"/>
+        <v>1.0071041666666625</v>
+      </c>
+      <c r="O13" s="4">
         <f t="shared" si="0"/>
-        <v>1.0071041666666625</v>
-      </c>
-      <c r="O13" s="4">
-        <f>STANDARDIZE(N13,Q$1,Q$2)</f>
         <v>-0.62886704729359444</v>
       </c>
       <c r="P13" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-1.0657664614317719E-2</v>
       </c>
     </row>
@@ -13045,15 +15662,15 @@
         <v>1.0291666666666599</v>
       </c>
       <c r="N14" s="2">
+        <f t="shared" si="1"/>
+        <v>1.0061874999999958</v>
+      </c>
+      <c r="O14" s="4">
         <f t="shared" si="0"/>
-        <v>1.0061874999999958</v>
-      </c>
-      <c r="O14" s="4">
-        <f>STANDARDIZE(N14,Q$1,Q$2)</f>
         <v>-0.68295595709515688</v>
       </c>
       <c r="P14" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-1.1574331280984396E-2</v>
       </c>
     </row>
@@ -13095,15 +15712,15 @@
         <v>1.0177499999999999</v>
       </c>
       <c r="N15" s="2">
+        <f t="shared" si="1"/>
+        <v>1.0031874999999975</v>
+      </c>
+      <c r="O15" s="4">
         <f t="shared" si="0"/>
-        <v>1.0031874999999975</v>
-      </c>
-      <c r="O15" s="4">
-        <f>STANDARDIZE(N15,Q$1,Q$2)</f>
         <v>-0.85997420735471564</v>
       </c>
       <c r="P15" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-1.4574331280982733E-2</v>
       </c>
     </row>
@@ -13145,15 +15762,15 @@
         <v>1.0240833333333299</v>
       </c>
       <c r="N16" s="2">
+        <f t="shared" si="1"/>
+        <v>0.997270833333329</v>
+      </c>
+      <c r="O16" s="4">
         <f t="shared" si="0"/>
-        <v>0.997270833333329</v>
-      </c>
-      <c r="O16" s="4">
-        <f>STANDARDIZE(N16,Q$1,Q$2)</f>
         <v>-1.2090935342558111</v>
       </c>
       <c r="P16" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-2.0490997947651191E-2</v>
       </c>
     </row>
@@ -13195,15 +15812,15 @@
         <v>1.0216666666666601</v>
       </c>
       <c r="N17" s="2">
+        <f t="shared" si="1"/>
+        <v>1.0057083333333301</v>
+      </c>
+      <c r="O17" s="4">
         <f t="shared" si="0"/>
-        <v>1.0057083333333301</v>
-      </c>
-      <c r="O17" s="4">
-        <f>STANDARDIZE(N17,Q$1,Q$2)</f>
         <v>-0.7112297054004616</v>
       </c>
       <c r="P17" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-1.2053497947650094E-2</v>
       </c>
     </row>
@@ -13245,15 +15862,15 @@
         <v>1.0500833333333299</v>
       </c>
       <c r="N18" s="2">
+        <f t="shared" si="1"/>
+        <v>1.0278958333333275</v>
+      </c>
+      <c r="O18" s="4">
         <f t="shared" si="0"/>
-        <v>1.0278958333333275</v>
-      </c>
-      <c r="O18" s="4">
-        <f>STANDARDIZE(N18,Q$1,Q$2)</f>
         <v>0.59796777047809502</v>
       </c>
       <c r="P18" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.0134002052347268E-2</v>
       </c>
     </row>
@@ -13295,15 +15912,15 @@
         <v>1.024</v>
       </c>
       <c r="N19" s="2">
+        <f t="shared" si="1"/>
+        <v>0.99983333333333224</v>
+      </c>
+      <c r="O19" s="4">
         <f t="shared" si="0"/>
-        <v>0.99983333333333224</v>
-      </c>
-      <c r="O19" s="4">
-        <f>STANDARDIZE(N19,Q$1,Q$2)</f>
         <v>-1.0578904454921629</v>
       </c>
       <c r="P19" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-1.7928497947647948E-2</v>
       </c>
     </row>
@@ -13345,15 +15962,15 @@
         <v>0.99774999999999903</v>
       </c>
       <c r="N20" s="2">
+        <f t="shared" si="1"/>
+        <v>0.98558333333333203</v>
+      </c>
+      <c r="O20" s="4">
         <f t="shared" si="0"/>
-        <v>0.98558333333333203</v>
-      </c>
-      <c r="O20" s="4">
-        <f>STANDARDIZE(N20,Q$1,Q$2)</f>
         <v>-1.8987271342255452</v>
       </c>
       <c r="P20" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-3.2178497947648155E-2</v>
       </c>
     </row>
@@ -13395,15 +16012,15 @@
         <v>1.0234999999999901</v>
       </c>
       <c r="N21" s="2">
+        <f t="shared" si="1"/>
+        <v>1.0283124999999949</v>
+      </c>
+      <c r="O21" s="4">
         <f t="shared" si="0"/>
-        <v>1.0283124999999949</v>
-      </c>
-      <c r="O21" s="4">
-        <f>STANDARDIZE(N21,Q$1,Q$2)</f>
         <v>0.62255363856975721</v>
       </c>
       <c r="P21" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.0550668719014666E-2</v>
       </c>
     </row>
@@ -13445,15 +16062,15 @@
         <v>1.0199166666666599</v>
       </c>
       <c r="N22" s="2">
+        <f t="shared" si="1"/>
+        <v>1.0262916666666639</v>
+      </c>
+      <c r="O22" s="4">
         <f t="shared" si="0"/>
-        <v>1.0262916666666639</v>
-      </c>
-      <c r="O22" s="4">
-        <f>STANDARDIZE(N22,Q$1,Q$2)</f>
         <v>0.50331217832554753</v>
       </c>
       <c r="P22" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8.5298353856837483E-3</v>
       </c>
     </row>
@@ -13495,15 +16112,15 @@
         <v>1.0046666666666599</v>
       </c>
       <c r="N23" s="2">
+        <f t="shared" si="1"/>
+        <v>1.0216041666666633</v>
+      </c>
+      <c r="O23" s="4">
         <f t="shared" si="0"/>
-        <v>1.0216041666666633</v>
-      </c>
-      <c r="O23" s="4">
-        <f>STANDARDIZE(N23,Q$1,Q$2)</f>
         <v>0.22672116229479697</v>
       </c>
       <c r="P23" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.8423353856831266E-3</v>
       </c>
     </row>
@@ -13545,15 +16162,15 @@
         <v>1.0113333333333301</v>
       </c>
       <c r="N24" s="2">
+        <f t="shared" si="1"/>
+        <v>1.0191666666666626</v>
+      </c>
+      <c r="O24" s="4">
         <f t="shared" si="0"/>
-        <v>1.0191666666666626</v>
-      </c>
-      <c r="O24" s="4">
-        <f>STANDARDIZE(N24,Q$1,Q$2)</f>
         <v>8.2893833958780999E-2</v>
       </c>
       <c r="P24" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.4048353856823681E-3</v>
       </c>
     </row>
@@ -13595,15 +16212,15 @@
         <v>1.0169999999999999</v>
       </c>
       <c r="N25" s="2">
+        <f t="shared" si="1"/>
+        <v>1.0101041666666646</v>
+      </c>
+      <c r="O25" s="4">
         <f t="shared" si="0"/>
-        <v>1.0101041666666646</v>
-      </c>
-      <c r="O25" s="4">
-        <f>STANDARDIZE(N25,Q$1,Q$2)</f>
         <v>-0.45184879703381298</v>
       </c>
       <c r="P25" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-7.6576646143156069E-3</v>
       </c>
     </row>
@@ -13645,15 +16262,15 @@
         <v>1.0337499999999999</v>
       </c>
       <c r="N26" s="2">
+        <f t="shared" si="1"/>
+        <v>1.0245624999999965</v>
+      </c>
+      <c r="O26" s="4">
         <f t="shared" si="0"/>
-        <v>1.0245624999999965</v>
-      </c>
-      <c r="O26" s="4">
-        <f>STANDARDIZE(N26,Q$1,Q$2)</f>
         <v>0.40128082574528251</v>
       </c>
       <c r="P26" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6.8006687190163007E-3</v>
       </c>
     </row>
@@ -13695,15 +16312,15 @@
         <v>1.0555000000000001</v>
       </c>
       <c r="N27" s="2">
+        <f t="shared" si="1"/>
+        <v>1.0401041666666651</v>
+      </c>
+      <c r="O27" s="4">
         <f t="shared" si="0"/>
-        <v>1.0401041666666651</v>
-      </c>
-      <c r="O27" s="4">
-        <f>STANDARDIZE(N27,Q$1,Q$2)</f>
         <v>1.3183337055627835</v>
       </c>
       <c r="P27" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.2342335385684864E-2</v>
       </c>
     </row>
@@ -13745,15 +16362,15 @@
         <v>1.04575</v>
       </c>
       <c r="N28" s="2">
+        <f t="shared" si="1"/>
+        <v>1.0390416666666649</v>
+      </c>
+      <c r="O28" s="4">
         <f t="shared" si="0"/>
-        <v>1.0390416666666649</v>
-      </c>
-      <c r="O28" s="4">
-        <f>STANDARDIZE(N28,Q$1,Q$2)</f>
         <v>1.2556397419291438</v>
       </c>
       <c r="P28" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.1279835385684676E-2</v>
       </c>
     </row>
@@ -13795,15 +16412,15 @@
         <v>1.04216666666666</v>
       </c>
       <c r="N29" s="2">
+        <f t="shared" si="1"/>
+        <v>1.0333468589374948</v>
+      </c>
+      <c r="O29" s="4">
         <f t="shared" si="0"/>
-        <v>1.0333468589374948</v>
-      </c>
-      <c r="O29" s="4">
-        <f>STANDARDIZE(N29,Q$1,Q$2)</f>
         <v>0.91961144200152467</v>
       </c>
       <c r="P29" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.5585027656514594E-2</v>
       </c>
     </row>
@@ -13845,15 +16462,15 @@
         <v>1.0125</v>
       </c>
       <c r="N30" s="2">
+        <f t="shared" si="1"/>
+        <v>1.0173815951666656</v>
+      </c>
+      <c r="O30" s="4">
         <f t="shared" si="0"/>
-        <v>1.0173815951666656</v>
-      </c>
-      <c r="O30" s="4">
-        <f>STANDARDIZE(N30,Q$1,Q$2)</f>
         <v>-2.2436243880499956E-2</v>
       </c>
       <c r="P30" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-3.8023611431459159E-4</v>
       </c>
     </row>
@@ -13895,15 +16512,15 @@
         <v>1.00708333333333</v>
       </c>
       <c r="N31" s="2">
+        <f t="shared" si="1"/>
+        <v>1.0213693587083308</v>
+      </c>
+      <c r="O31" s="4">
         <f t="shared" si="0"/>
-        <v>1.0213693587083308</v>
-      </c>
-      <c r="O31" s="4">
-        <f>STANDARDIZE(N31,Q$1,Q$2)</f>
         <v>0.2128660643177748</v>
       </c>
       <c r="P31" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.6075274273505986E-3</v>
       </c>
     </row>
@@ -13945,15 +16562,15 @@
         <v>1.0028333333333299</v>
       </c>
       <c r="N32" s="2">
+        <f t="shared" si="1"/>
+        <v>1.0182929276874972</v>
+      </c>
+      <c r="O32" s="4">
         <f t="shared" si="0"/>
-        <v>1.0182929276874972</v>
-      </c>
-      <c r="O32" s="4">
-        <f>STANDARDIZE(N32,Q$1,Q$2)</f>
         <v>3.133791886694659E-2</v>
       </c>
       <c r="P32" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5.3109640651705092E-4</v>
       </c>
     </row>
@@ -13995,15 +16612,15 @@
         <v>1.0045833333333301</v>
       </c>
       <c r="N33" s="2">
+        <f t="shared" si="1"/>
+        <v>1.023453438874995</v>
+      </c>
+      <c r="O33" s="4">
         <f t="shared" si="0"/>
-        <v>1.023453438874995</v>
-      </c>
-      <c r="O33" s="4">
-        <f>STANDARDIZE(N33,Q$1,Q$2)</f>
         <v>0.33583947248568996</v>
       </c>
       <c r="P33" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5.6916075940147692E-3</v>
       </c>
     </row>
@@ -14045,15 +16662,15 @@
         <v>1.022</v>
       </c>
       <c r="N34" s="2">
+        <f t="shared" si="1"/>
+        <v>1.0127342579166652</v>
+      </c>
+      <c r="O34" s="4">
         <f t="shared" si="0"/>
-        <v>1.0127342579166652</v>
-      </c>
-      <c r="O34" s="4">
-        <f>STANDARDIZE(N34,Q$1,Q$2)</f>
         <v>-0.29665741333436768</v>
       </c>
       <c r="P34" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-5.02757336431503E-3</v>
       </c>
     </row>
@@ -14095,15 +16712,15 @@
         <v>1.0235000000000001</v>
       </c>
       <c r="N35" s="2">
+        <f t="shared" si="1"/>
+        <v>1.0200966635833333</v>
+      </c>
+      <c r="O35" s="4">
         <f t="shared" si="0"/>
-        <v>1.0200966635833333</v>
-      </c>
-      <c r="O35" s="4">
-        <f>STANDARDIZE(N35,Q$1,Q$2)</f>
         <v>0.1377693096040904</v>
       </c>
       <c r="P35" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.3348323023530959E-3</v>
       </c>
     </row>
@@ -14136,11 +16753,11 @@
         <v>1.04508333333333</v>
       </c>
       <c r="N36" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0432222222222201</v>
       </c>
       <c r="P36" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.5460390941239863E-2</v>
       </c>
     </row>
@@ -14173,11 +16790,11 @@
         <v>1.02725</v>
       </c>
       <c r="N37" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.02322222222222</v>
       </c>
       <c r="P37" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5.4603909412398455E-3</v>
       </c>
     </row>
@@ -14210,11 +16827,11 @@
         <v>1.05941666666666</v>
       </c>
       <c r="N38" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0366944444444399</v>
       </c>
       <c r="P38" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.8932613163459733E-2</v>
       </c>
     </row>
@@ -14247,11 +16864,11 @@
         <v>1.0627500000000001</v>
       </c>
       <c r="N39" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0418333333333301</v>
       </c>
       <c r="P39" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.4071502052349869E-2</v>
       </c>
     </row>
@@ -14284,11 +16901,11 @@
         <v>1.0458333333333301</v>
       </c>
       <c r="N40" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0279999999999987</v>
       </c>
       <c r="P40" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.0238168719018503E-2</v>
       </c>
     </row>
@@ -14321,11 +16938,11 @@
         <v>1.0496666666666601</v>
       </c>
       <c r="N41" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0332777777777744</v>
       </c>
       <c r="P41" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.551594649679422E-2</v>
       </c>
     </row>
@@ -14358,11 +16975,11 @@
         <v>1.0527500000000001</v>
       </c>
       <c r="N42" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0329444444444433</v>
       </c>
       <c r="P42" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.5182613163463143E-2</v>
       </c>
     </row>
@@ -14395,11 +17012,11 @@
         <v>1.02983333333333</v>
       </c>
       <c r="N43" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0113888888888869</v>
       </c>
       <c r="P43" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-6.3729423920932948E-3</v>
       </c>
     </row>
@@ -14432,11 +17049,11 @@
         <v>1.0322499999999999</v>
       </c>
       <c r="N44" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0190555555555501</v>
       </c>
       <c r="P44" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2937242745698629E-3</v>
       </c>
     </row>
@@ -14469,11 +17086,11 @@
         <v>1.0245833333333301</v>
       </c>
       <c r="N45" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0101666666666633</v>
       </c>
       <c r="P45" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-7.5951646143168627E-3</v>
       </c>
     </row>
@@ -14506,11 +17123,11 @@
         <v>1.036</v>
       </c>
       <c r="N46" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0155277777777776</v>
       </c>
       <c r="P46" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-2.2340535032026043E-3</v>
       </c>
     </row>
@@ -14543,11 +17160,11 @@
         <v>1.03866666666666</v>
       </c>
       <c r="N47" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0228333333333299</v>
       </c>
       <c r="P47" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5.0715020523497412E-3</v>
       </c>
     </row>
@@ -14580,11 +17197,11 @@
         <v>1.0373333333333301</v>
       </c>
       <c r="N48" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0286944444444435</v>
       </c>
       <c r="P48" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.0932613163463278E-2</v>
       </c>
     </row>
@@ -14617,11 +17234,11 @@
         <v>1.04558333333333</v>
       </c>
       <c r="N49" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0189444444444422</v>
       </c>
       <c r="P49" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.1826131634620207E-3</v>
       </c>
     </row>
@@ -14654,11 +17271,11 @@
         <v>1.0302499999999899</v>
       </c>
       <c r="N50" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.02044444444444</v>
       </c>
       <c r="P50" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.6826131634598571E-3</v>
       </c>
     </row>
@@ -14691,11 +17308,11 @@
         <v>1.0254999999999901</v>
       </c>
       <c r="N51" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0211944444444399</v>
       </c>
       <c r="P51" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.4326131634596635E-3</v>
       </c>
     </row>
@@ -14728,11 +17345,11 @@
         <v>1.0293333333333301</v>
       </c>
       <c r="N52" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0051944444444429</v>
       </c>
       <c r="P52" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-1.2567386836537242E-2</v>
       </c>
     </row>
@@ -14765,11 +17382,11 @@
         <v>1.0115833333333299</v>
       </c>
       <c r="N53" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0075277777777754</v>
       </c>
       <c r="P53" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-1.0234053503204832E-2</v>
       </c>
     </row>
@@ -14802,11 +17419,11 @@
         <v>1.0285</v>
       </c>
       <c r="N54" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0187499999999967</v>
       </c>
       <c r="P54" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9.8816871901652448E-4</v>
       </c>
     </row>
@@ -14839,11 +17456,11 @@
         <v>1.0211666666666599</v>
       </c>
       <c r="N55" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0202499999999965</v>
       </c>
       <c r="P55" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.4881687190163593E-3</v>
       </c>
     </row>
@@ -14876,11 +17493,11 @@
         <v>1.0297499999999999</v>
       </c>
       <c r="N56" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0256944444444434</v>
       </c>
       <c r="P56" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7.9326131634631647E-3</v>
       </c>
     </row>
@@ -14913,11 +17530,11 @@
         <v>1.03033333333333</v>
       </c>
       <c r="N57" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0322222222222199</v>
       </c>
       <c r="P57" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.4460390941239742E-2</v>
       </c>
     </row>
@@ -14950,11 +17567,11 @@
         <v>1.0220833333333299</v>
       </c>
       <c r="N58" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0246666666666633</v>
       </c>
       <c r="P58" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6.9048353856830946E-3</v>
       </c>
     </row>
@@ -14987,11 +17604,11 @@
         <v>1.0251666666666599</v>
       </c>
       <c r="N59" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0240277777777733</v>
       </c>
       <c r="P59" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6.2659464967931289E-3</v>
       </c>
     </row>
@@ -15024,11 +17641,11 @@
         <v>1.0249999999999999</v>
       </c>
       <c r="N60" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0192499999999967</v>
       </c>
       <c r="P60" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.4881687190164694E-3</v>
       </c>
     </row>
@@ -15061,11 +17678,11 @@
         <v>1.04958333333333</v>
       </c>
       <c r="N61" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0478333333333301</v>
       </c>
       <c r="P61" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.0071502052349874E-2</v>
       </c>
     </row>
@@ -15098,11 +17715,11 @@
         <v>1.032</v>
       </c>
       <c r="N62" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0421944444444433</v>
       </c>
       <c r="P62" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.4432613163463124E-2</v>
       </c>
     </row>
@@ -15135,11 +17752,11 @@
         <v>1.03291666666666</v>
       </c>
       <c r="N63" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0393508768333266</v>
       </c>
       <c r="P63" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.158904555234642E-2</v>
       </c>
     </row>
@@ -15163,11 +17780,11 @@
         <v>1.0175000000000001</v>
       </c>
       <c r="N64" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0269166666666649</v>
       </c>
       <c r="P64" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9.1548353856847342E-3</v>
       </c>
     </row>
@@ -15191,11 +17808,11 @@
         <v>1.0302500000000001</v>
       </c>
       <c r="N65" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0355833333333302</v>
       </c>
       <c r="P65" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.7821502052350002E-2</v>
       </c>
     </row>
@@ -15219,11 +17836,11 @@
         <v>1.0385833333333301</v>
       </c>
       <c r="N66" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.050749999999995</v>
       </c>
       <c r="P66" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.2988168719014777E-2</v>
       </c>
     </row>
@@ -15234,16 +17851,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D450D66-8CE6-424E-B1F2-F32778C5AA83}">
-  <dimension ref="A1:V36"/>
+  <dimension ref="A1:Y36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="7.21875" customWidth="1"/>
     <col min="4" max="4" width="6.5546875" customWidth="1"/>
-    <col min="5" max="5" width="7.88671875" customWidth="1"/>
-    <col min="6" max="6" width="6.5546875" customWidth="1"/>
+    <col min="5" max="5" width="6.109375" customWidth="1"/>
+    <col min="6" max="6" width="7.88671875" customWidth="1"/>
+    <col min="7" max="8" width="7.109375" customWidth="1"/>
+    <col min="9" max="9" width="6.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -15251,20 +17870,29 @@
         <v>9</v>
       </c>
       <c r="C1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D1" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="E1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1" s="4">
+        <v>35</v>
+      </c>
+      <c r="F1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="4">
         <f>AVERAGE(B2:B36)</f>
         <v>365.18504901960779</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2015</v>
       </c>
@@ -15272,25 +17900,37 @@
         <v>259.74166666666667</v>
       </c>
       <c r="C2" s="3">
-        <f>B2-F$1</f>
+        <f>B2-I$1</f>
         <v>-105.44338235294111</v>
       </c>
       <c r="D2" s="4">
-        <f>STANDARDIZE(B2,F$1,F$2)</f>
+        <f t="shared" ref="D2:D35" si="0">STANDARDIZE(B2,I$1,I$2)</f>
         <v>-1.0751984741460796</v>
       </c>
       <c r="E2" s="5">
         <v>-2.0659110372486018</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="5">
+        <f>AVERAGE(D2:D3)</f>
+        <v>-0.7358107533054159</v>
+      </c>
+      <c r="G2" s="5">
+        <f>AVERAGE(E2:E3)</f>
+        <v>-2.3670879213708833</v>
+      </c>
+      <c r="H2" s="5">
+        <f>AVERAGE(E2:E4)</f>
+        <v>-2.44125529011392</v>
+      </c>
+      <c r="I2" s="4">
         <f>_xlfn.STDEV.S(B2:B36)</f>
         <v>98.068761152850442</v>
       </c>
-      <c r="O2" t="s">
+      <c r="R2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2014</v>
       </c>
@@ -15298,21 +17938,33 @@
         <v>326.30833333333334</v>
       </c>
       <c r="C3" s="3">
-        <f t="shared" ref="C3:C35" si="0">B3-F$1</f>
+        <f t="shared" ref="C3:C35" si="1">B3-I$1</f>
         <v>-38.876715686274451</v>
       </c>
       <c r="D3" s="4">
-        <f>STANDARDIZE(B3,F$1,F$2)</f>
+        <f t="shared" si="0"/>
         <v>-0.39642303246475213</v>
       </c>
       <c r="E3" s="5">
         <v>-2.6682648054931648</v>
       </c>
-      <c r="O3" t="s">
+      <c r="F3" s="5">
+        <f>AVERAGE(D2:D4)</f>
+        <v>-0.73232680324170352</v>
+      </c>
+      <c r="G3" s="5">
+        <f>AVERAGE(E2:E4)</f>
+        <v>-2.44125529011392</v>
+      </c>
+      <c r="H3" s="5">
+        <f>AVERAGE(E2:E5)</f>
+        <v>-2.2499977245845257</v>
+      </c>
+      <c r="R3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2013</v>
       </c>
@@ -15320,21 +17972,33 @@
         <v>294.05</v>
       </c>
       <c r="C4" s="3">
+        <f t="shared" si="1"/>
+        <v>-71.135049019607777</v>
+      </c>
+      <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>-71.135049019607777</v>
-      </c>
-      <c r="D4" s="4">
-        <f>STANDARDIZE(B4,F$1,F$2)</f>
         <v>-0.72535890311427864</v>
       </c>
       <c r="E4" s="5">
         <v>-2.5895900275999928</v>
       </c>
-      <c r="O4" t="s">
+      <c r="F4" s="5">
+        <f t="shared" ref="F4:F34" si="2">AVERAGE(D3:D5)</f>
+        <v>-0.40353255657850678</v>
+      </c>
+      <c r="G4" s="5">
+        <f t="shared" ref="G4:G34" si="3">AVERAGE(E3:E5)</f>
+        <v>-2.3113599536965004</v>
+      </c>
+      <c r="H4" s="5">
+        <f>AVERAGE(E2:E6)</f>
+        <v>-1.9887114114408591</v>
+      </c>
+      <c r="R4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2012</v>
       </c>
@@ -15342,18 +18006,30 @@
         <v>356.47499999999997</v>
       </c>
       <c r="C5" s="3">
+        <f t="shared" si="1"/>
+        <v>-8.7100490196078226</v>
+      </c>
+      <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>-8.7100490196078226</v>
-      </c>
-      <c r="D5" s="4">
-        <f>STANDARDIZE(B5,F$1,F$2)</f>
         <v>-8.8815734156489426E-2</v>
       </c>
       <c r="E5" s="5">
         <v>-1.676225027996344</v>
       </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="F5" s="5">
+        <f t="shared" si="2"/>
+        <v>0.24085658122195261</v>
+      </c>
+      <c r="G5" s="5">
+        <f t="shared" si="3"/>
+        <v>-1.7364604048208425</v>
+      </c>
+      <c r="H5" s="5">
+        <f t="shared" ref="H5:H33" si="4">AVERAGE(E3:E7)</f>
+        <v>-1.7799773913430006</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2011</v>
       </c>
@@ -15361,18 +18037,30 @@
         <v>515.89166666666677</v>
       </c>
       <c r="C6" s="3">
+        <f t="shared" si="1"/>
+        <v>150.70661764705898</v>
+      </c>
+      <c r="D6" s="4">
         <f t="shared" si="0"/>
-        <v>150.70661764705898</v>
-      </c>
-      <c r="D6" s="4">
-        <f>STANDARDIZE(B6,F$1,F$2)</f>
         <v>1.5367443809366259</v>
       </c>
       <c r="E6" s="5">
         <v>-0.94356615886619133</v>
       </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="F6" s="5">
+        <f t="shared" si="2"/>
+        <v>0.82307278902364145</v>
+      </c>
+      <c r="G6" s="5">
+        <f t="shared" si="3"/>
+        <v>-1.2140107078739488</v>
+      </c>
+      <c r="H6" s="5">
+        <f t="shared" si="4"/>
+        <v>-1.5478867965581258</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2010</v>
       </c>
@@ -15380,18 +18068,30 @@
         <v>465.34166666666653</v>
       </c>
       <c r="C7" s="3">
+        <f t="shared" si="1"/>
+        <v>100.15661764705874</v>
+      </c>
+      <c r="D7" s="4">
         <f t="shared" si="0"/>
-        <v>100.15661764705874</v>
-      </c>
-      <c r="D7" s="4">
-        <f>STANDARDIZE(B7,F$1,F$2)</f>
         <v>1.0212897202907882</v>
       </c>
       <c r="E7" s="5">
         <v>-1.022240936759311</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="F7" s="5">
+        <f t="shared" si="2"/>
+        <v>1.0364718116253411</v>
+      </c>
+      <c r="G7" s="5">
+        <f t="shared" si="3"/>
+        <v>-1.157872975731431</v>
+      </c>
+      <c r="H7" s="5">
+        <f t="shared" si="4"/>
+        <v>-1.199996763061741</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2009</v>
       </c>
@@ -15399,21 +18099,33 @@
         <v>419.25833333333338</v>
       </c>
       <c r="C8" s="3">
+        <f t="shared" si="1"/>
+        <v>54.073284313725594</v>
+      </c>
+      <c r="D8" s="4">
         <f t="shared" si="0"/>
-        <v>54.073284313725594</v>
-      </c>
-      <c r="D8" s="4">
-        <f>STANDARDIZE(B8,F$1,F$2)</f>
         <v>0.5513813336486092</v>
       </c>
       <c r="E8" s="5">
         <v>-1.5078118315687905</v>
       </c>
-      <c r="O8" t="s">
+      <c r="F8" s="5">
+        <f t="shared" si="2"/>
+        <v>1.188094451389994</v>
+      </c>
+      <c r="G8" s="5">
+        <f t="shared" si="3"/>
+        <v>-1.1267308761487236</v>
+      </c>
+      <c r="H8" s="5">
+        <f t="shared" si="4"/>
+        <v>-0.97798637419445544</v>
+      </c>
+      <c r="R8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>2008</v>
       </c>
@@ -15421,18 +18133,30 @@
         <v>560.5</v>
       </c>
       <c r="C9" s="3">
+        <f t="shared" si="1"/>
+        <v>195.31495098039221</v>
+      </c>
+      <c r="D9" s="4">
         <f t="shared" si="0"/>
-        <v>195.31495098039221</v>
-      </c>
-      <c r="D9" s="4">
-        <f>STANDARDIZE(B9,F$1,F$2)</f>
         <v>1.9916123002305841</v>
       </c>
       <c r="E9" s="5">
         <v>-0.85013986011806908</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="F9" s="5">
+        <f t="shared" si="2"/>
+        <v>1.3475630599973165</v>
+      </c>
+      <c r="G9" s="5">
+        <f t="shared" si="3"/>
+        <v>-0.97470825844892506</v>
+      </c>
+      <c r="H9" s="5">
+        <f t="shared" si="4"/>
+        <v>-0.87988876050888332</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2007</v>
       </c>
@@ -15440,42 +18164,54 @@
         <v>512.25833333333333</v>
       </c>
       <c r="C10" s="3">
+        <f t="shared" si="1"/>
+        <v>147.07328431372554</v>
+      </c>
+      <c r="D10" s="4">
         <f t="shared" si="0"/>
-        <v>147.07328431372554</v>
-      </c>
-      <c r="D10" s="4">
-        <f>STANDARDIZE(B10,F$1,F$2)</f>
         <v>1.4996955461127566</v>
       </c>
       <c r="E10" s="5">
         <v>-0.56617308365991559</v>
       </c>
-      <c r="O10" s="6" t="s">
+      <c r="F10" s="5">
+        <f t="shared" si="2"/>
+        <v>1.5622083736787176</v>
+      </c>
+      <c r="G10" s="5">
+        <f t="shared" si="3"/>
+        <v>-0.62313034473877149</v>
+      </c>
+      <c r="H10" s="5">
+        <f t="shared" si="4"/>
+        <v>-0.84153480628597888</v>
+      </c>
+      <c r="R10" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="P10" s="7" t="s">
+      <c r="S10" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="Q10" s="7" t="s">
+      <c r="T10" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="R10" s="7" t="s">
+      <c r="U10" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="S10" s="7" t="s">
+      <c r="V10" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="T10" s="7" t="s">
+      <c r="W10" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="U10" s="7" t="s">
+      <c r="X10" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="V10" s="7" t="s">
+      <c r="Y10" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2006</v>
       </c>
@@ -15483,42 +18219,54 @@
         <v>482.4083333333333</v>
       </c>
       <c r="C11" s="3">
+        <f t="shared" si="1"/>
+        <v>117.22328431372551</v>
+      </c>
+      <c r="D11" s="4">
         <f t="shared" si="0"/>
-        <v>117.22328431372551</v>
-      </c>
-      <c r="D11" s="4">
-        <f>STANDARDIZE(B11,F$1,F$2)</f>
         <v>1.195317274692812</v>
       </c>
       <c r="E11" s="5">
         <v>-0.45307809043832992</v>
       </c>
-      <c r="O11" s="8" t="s">
+      <c r="F11" s="5">
+        <f t="shared" si="2"/>
+        <v>1.0227909345458848</v>
+      </c>
+      <c r="G11" s="5">
+        <f t="shared" si="3"/>
+        <v>-0.61657411324767819</v>
+      </c>
+      <c r="H11" s="5">
+        <f t="shared" si="4"/>
+        <v>-0.66574584943093962</v>
+      </c>
+      <c r="R11" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="P11" s="10">
+      <c r="S11" s="8">
         <v>34</v>
       </c>
-      <c r="Q11" s="10">
+      <c r="T11" s="8">
         <v>0</v>
       </c>
-      <c r="R11" s="10">
+      <c r="U11" s="8">
         <v>34</v>
       </c>
-      <c r="S11" s="12">
+      <c r="V11" s="10">
         <v>-2.1226778018383334</v>
       </c>
-      <c r="T11" s="12">
+      <c r="W11" s="10">
         <v>1.9916123002305841</v>
       </c>
-      <c r="U11" s="12">
+      <c r="X11" s="10">
         <v>5.4817261840867104E-16</v>
       </c>
-      <c r="V11" s="12">
+      <c r="Y11" s="10">
         <v>0.99999999999999678</v>
       </c>
     </row>
-    <row r="12" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>2005</v>
       </c>
@@ -15526,42 +18274,54 @@
         <v>401.79999999999995</v>
       </c>
       <c r="C12" s="3">
+        <f t="shared" si="1"/>
+        <v>36.614950980392166</v>
+      </c>
+      <c r="D12" s="4">
         <f t="shared" si="0"/>
-        <v>36.614950980392166</v>
-      </c>
-      <c r="D12" s="4">
-        <f>STANDARDIZE(B12,F$1,F$2)</f>
         <v>0.37335998283208582</v>
       </c>
       <c r="E12" s="5">
         <v>-0.83047116564478918</v>
       </c>
-      <c r="O12" s="9" t="s">
+      <c r="F12" s="5">
+        <f t="shared" si="2"/>
+        <v>0.54192085136177981</v>
+      </c>
+      <c r="G12" s="5">
+        <f t="shared" si="3"/>
+        <v>-0.63747210112557118</v>
+      </c>
+      <c r="H12" s="5">
+        <f t="shared" si="4"/>
+        <v>-0.63230906882635707</v>
+      </c>
+      <c r="R12" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="P12" s="11">
+      <c r="S12" s="9">
         <v>34</v>
       </c>
-      <c r="Q12" s="11">
+      <c r="T12" s="9">
         <v>0</v>
       </c>
-      <c r="R12" s="11">
+      <c r="U12" s="9">
         <v>34</v>
       </c>
-      <c r="S12" s="13">
+      <c r="V12" s="11">
         <v>-2.6682648054931648</v>
       </c>
-      <c r="T12" s="13">
+      <c r="W12" s="11">
         <v>1.3183337055627835</v>
       </c>
-      <c r="U12" s="13">
+      <c r="X12" s="11">
         <v>-0.4807948660770418</v>
       </c>
-      <c r="V12" s="13">
+      <c r="Y12" s="11">
         <v>1.0050348901743253</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2004</v>
       </c>
@@ -15569,18 +18329,30 @@
         <v>370.78333333333336</v>
       </c>
       <c r="C13" s="3">
+        <f t="shared" si="1"/>
+        <v>5.5982843137255713</v>
+      </c>
+      <c r="D13" s="4">
         <f t="shared" si="0"/>
-        <v>5.5982843137255713</v>
-      </c>
-      <c r="D13" s="4">
-        <f>STANDARDIZE(B13,F$1,F$2)</f>
         <v>5.7085296560441492E-2</v>
       </c>
       <c r="E13" s="5">
         <v>-0.62886704729359444</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="F13" s="5">
+        <f t="shared" si="2"/>
+        <v>0.14959408443104774</v>
+      </c>
+      <c r="G13" s="5">
+        <f t="shared" si="3"/>
+        <v>-0.71409805667784687</v>
+      </c>
+      <c r="H13" s="5">
+        <f t="shared" si="4"/>
+        <v>-0.69106929356531721</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2003</v>
       </c>
@@ -15588,18 +18360,30 @@
         <v>366.98333333333335</v>
       </c>
       <c r="C14" s="3">
+        <f t="shared" si="1"/>
+        <v>1.79828431372556</v>
+      </c>
+      <c r="D14" s="4">
         <f t="shared" si="0"/>
-        <v>1.79828431372556</v>
-      </c>
-      <c r="D14" s="4">
-        <f>STANDARDIZE(B14,F$1,F$2)</f>
         <v>1.833697390061597E-2</v>
       </c>
       <c r="E14" s="5">
         <v>-0.68295595709515688</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="F14" s="5">
+        <f t="shared" si="2"/>
+        <v>1.2813638433754894E-2</v>
+      </c>
+      <c r="G14" s="5">
+        <f t="shared" si="3"/>
+        <v>-0.72393240391448899</v>
+      </c>
+      <c r="H14" s="5">
+        <f t="shared" si="4"/>
+        <v>-0.84227238232881363</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2002</v>
       </c>
@@ -15607,21 +18391,33 @@
         <v>361.55833333333334</v>
       </c>
       <c r="C15" s="3">
+        <f t="shared" si="1"/>
+        <v>-3.6267156862744514</v>
+      </c>
+      <c r="D15" s="4">
         <f t="shared" si="0"/>
-        <v>-3.6267156862744514</v>
-      </c>
-      <c r="D15" s="4">
-        <f>STANDARDIZE(B15,F$1,F$2)</f>
         <v>-3.6981355159792777E-2</v>
       </c>
       <c r="E15" s="5">
         <v>-0.85997420735471564</v>
       </c>
-      <c r="O15" t="s">
+      <c r="F15" s="5">
+        <f t="shared" si="2"/>
+        <v>-0.27927167097276545</v>
+      </c>
+      <c r="G15" s="5">
+        <f t="shared" si="3"/>
+        <v>-0.91734123290189462</v>
+      </c>
+      <c r="H15" s="5">
+        <f t="shared" si="4"/>
+        <v>-0.818424090279948</v>
+      </c>
+      <c r="R15" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>2001</v>
       </c>
@@ -15629,18 +18425,30 @@
         <v>284.84999999999997</v>
       </c>
       <c r="C16" s="3">
+        <f t="shared" si="1"/>
+        <v>-80.335049019607823</v>
+      </c>
+      <c r="D16" s="4">
         <f t="shared" si="0"/>
-        <v>-80.335049019607823</v>
-      </c>
-      <c r="D16" s="4">
-        <f>STANDARDIZE(B16,F$1,F$2)</f>
         <v>-0.81917063165911952</v>
       </c>
       <c r="E16" s="5">
         <v>-1.2090935342558111</v>
       </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="F16" s="5">
+        <f t="shared" si="2"/>
+        <v>0.21287168152318961</v>
+      </c>
+      <c r="G16" s="5">
+        <f t="shared" si="3"/>
+        <v>-0.92676581567032945</v>
+      </c>
+      <c r="H16" s="5">
+        <f t="shared" si="4"/>
+        <v>-0.57305712672561016</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2000</v>
       </c>
@@ -15648,27 +18456,39 @@
         <v>511.77500000000003</v>
       </c>
       <c r="C17" s="3">
+        <f t="shared" si="1"/>
+        <v>146.58995098039225</v>
+      </c>
+      <c r="D17" s="4">
         <f t="shared" si="0"/>
-        <v>146.58995098039225</v>
-      </c>
-      <c r="D17" s="4">
-        <f>STANDARDIZE(B17,F$1,F$2)</f>
         <v>1.4947670313884811</v>
       </c>
       <c r="E17" s="5">
         <v>-0.7112297054004616</v>
       </c>
-      <c r="O17" s="6" t="s">
+      <c r="F17" s="5">
+        <f t="shared" si="2"/>
+        <v>0.81202611808991987</v>
+      </c>
+      <c r="G17" s="5">
+        <f t="shared" si="3"/>
+        <v>-0.44078515639272592</v>
+      </c>
+      <c r="H17" s="5">
+        <f t="shared" si="4"/>
+        <v>-0.64804402440501119</v>
+      </c>
+      <c r="R17" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="P17" s="7" t="s">
+      <c r="S17" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="Q17" s="7" t="s">
+      <c r="T17" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>1999</v>
       </c>
@@ -15676,27 +18496,39 @@
         <v>537.83333333333337</v>
       </c>
       <c r="C18" s="3">
+        <f t="shared" si="1"/>
+        <v>172.64828431372558</v>
+      </c>
+      <c r="D18" s="4">
         <f t="shared" si="0"/>
-        <v>172.64828431372558</v>
-      </c>
-      <c r="D18" s="4">
-        <f>STANDARDIZE(B18,F$1,F$2)</f>
         <v>1.7604819545403978</v>
       </c>
       <c r="E18" s="5">
         <v>0.59796777047809502</v>
       </c>
-      <c r="O18" s="14" t="s">
+      <c r="F18" s="5">
+        <f t="shared" si="2"/>
+        <v>1.0618225051783703</v>
+      </c>
+      <c r="G18" s="5">
+        <f t="shared" si="3"/>
+        <v>-0.39038412680484313</v>
+      </c>
+      <c r="H18" s="5">
+        <f t="shared" si="4"/>
+        <v>-0.85579460977917721</v>
+      </c>
+      <c r="R18" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="P18" s="15">
+      <c r="S18" s="13">
         <v>1</v>
       </c>
-      <c r="Q18" s="12">
+      <c r="T18" s="10">
         <v>0.1022248488675736</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>1998</v>
       </c>
@@ -15704,27 +18536,39 @@
         <v>358.34166666666664</v>
       </c>
       <c r="C19" s="3">
+        <f t="shared" si="1"/>
+        <v>-6.8433823529411484</v>
+      </c>
+      <c r="D19" s="4">
         <f t="shared" si="0"/>
-        <v>-6.8433823529411484</v>
-      </c>
-      <c r="D19" s="4">
-        <f>STANDARDIZE(B19,F$1,F$2)</f>
         <v>-6.97814703937681E-2</v>
       </c>
       <c r="E19" s="5">
         <v>-1.0578904454921629</v>
       </c>
-      <c r="O19" s="16" t="s">
+      <c r="F19" s="5">
+        <f t="shared" si="2"/>
+        <v>5.1788559471707796E-2</v>
+      </c>
+      <c r="G19" s="5">
+        <f t="shared" si="3"/>
+        <v>-0.78621660307987096</v>
+      </c>
+      <c r="H19" s="5">
+        <f t="shared" si="4"/>
+        <v>-0.48946517521406357</v>
+      </c>
+      <c r="R19" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="P19" s="13">
+      <c r="S19" s="11">
         <v>0.1022248488675736</v>
       </c>
-      <c r="Q19" s="17">
+      <c r="T19" s="15">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>1997</v>
       </c>
@@ -15732,21 +18576,33 @@
         <v>214.61666666666665</v>
       </c>
       <c r="C20" s="3">
+        <f t="shared" si="1"/>
+        <v>-150.56838235294114</v>
+      </c>
+      <c r="D20" s="4">
         <f t="shared" si="0"/>
-        <v>-150.56838235294114</v>
-      </c>
-      <c r="D20" s="4">
-        <f>STANDARDIZE(B20,F$1,F$2)</f>
         <v>-1.5353348057315064</v>
       </c>
       <c r="E20" s="5">
         <v>-1.8987271342255452</v>
       </c>
-      <c r="O20" s="18" t="s">
+      <c r="F20" s="5">
+        <f t="shared" si="2"/>
+        <v>-0.39146619294321039</v>
+      </c>
+      <c r="G20" s="5">
+        <f t="shared" si="3"/>
+        <v>-0.77802131371598371</v>
+      </c>
+      <c r="H20" s="5">
+        <f t="shared" si="4"/>
+        <v>-0.24655679846886161</v>
+      </c>
+      <c r="R20" s="16" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>1996</v>
       </c>
@@ -15754,18 +18610,30 @@
         <v>407.42499999999995</v>
       </c>
       <c r="C21" s="3">
+        <f t="shared" si="1"/>
+        <v>42.239950980392166</v>
+      </c>
+      <c r="D21" s="4">
         <f t="shared" si="0"/>
-        <v>42.239950980392166</v>
-      </c>
-      <c r="D21" s="4">
-        <f>STANDARDIZE(B21,F$1,F$2)</f>
         <v>0.43071769729564319</v>
       </c>
       <c r="E21" s="5">
         <v>0.62255363856975721</v>
       </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="F21" s="5">
+        <f t="shared" si="2"/>
+        <v>-0.27867685023018041</v>
+      </c>
+      <c r="G21" s="5">
+        <f t="shared" si="3"/>
+        <v>-0.25762043911008015</v>
+      </c>
+      <c r="H21" s="5">
+        <f t="shared" si="4"/>
+        <v>-0.32080612010552134</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>1995</v>
       </c>
@@ -15773,18 +18641,30 @@
         <v>391.52500000000003</v>
       </c>
       <c r="C22" s="3">
+        <f t="shared" si="1"/>
+        <v>26.339950980392246</v>
+      </c>
+      <c r="D22" s="4">
         <f t="shared" si="0"/>
-        <v>26.339950980392246</v>
-      </c>
-      <c r="D22" s="4">
-        <f>STANDARDIZE(B22,F$1,F$2)</f>
         <v>0.26858655774532192</v>
       </c>
       <c r="E22" s="5">
         <v>0.50331217832554753</v>
       </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="F22" s="5">
+        <f t="shared" si="2"/>
+        <v>0.30045195466951985</v>
+      </c>
+      <c r="G22" s="5">
+        <f t="shared" si="3"/>
+        <v>0.4508623263967006</v>
+      </c>
+      <c r="H22" s="5">
+        <f t="shared" si="4"/>
+        <v>-9.2649264215332483E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>1994</v>
       </c>
@@ -15792,21 +18672,33 @@
         <v>384.99999999999994</v>
       </c>
       <c r="C23" s="3">
+        <f t="shared" si="1"/>
+        <v>19.814950980392155</v>
+      </c>
+      <c r="D23" s="4">
         <f t="shared" si="0"/>
-        <v>19.814950980392155</v>
-      </c>
-      <c r="D23" s="4">
-        <f>STANDARDIZE(B23,F$1,F$2)</f>
         <v>0.20205160896759444</v>
       </c>
       <c r="E23" s="5">
         <v>0.22672116229479697</v>
       </c>
-      <c r="O23" t="s">
+      <c r="F23" s="5">
+        <f t="shared" si="2"/>
+        <v>1.7458905185371226E-2</v>
+      </c>
+      <c r="G23" s="5">
+        <f t="shared" si="3"/>
+        <v>0.2709757248597085</v>
+      </c>
+      <c r="H23" s="5">
+        <f t="shared" si="4"/>
+        <v>0.19672640322301396</v>
+      </c>
+      <c r="R23" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>1993</v>
       </c>
@@ -15814,18 +18706,30 @@
         <v>324.16666666666669</v>
       </c>
       <c r="C24" s="3">
+        <f t="shared" si="1"/>
+        <v>-41.018382352941103</v>
+      </c>
+      <c r="D24" s="4">
         <f t="shared" si="0"/>
-        <v>-41.018382352941103</v>
-      </c>
-      <c r="D24" s="4">
-        <f>STANDARDIZE(B24,F$1,F$2)</f>
         <v>-0.41826145115680269</v>
       </c>
       <c r="E24" s="5">
         <v>8.2893833958780999E-2</v>
       </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="F24" s="5">
+        <f t="shared" si="2"/>
+        <v>-0.46751827360229736</v>
+      </c>
+      <c r="G24" s="5">
+        <f t="shared" si="3"/>
+        <v>-4.7411266926745001E-2</v>
+      </c>
+      <c r="H24" s="5">
+        <f t="shared" si="4"/>
+        <v>0.152471840658119</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>1992</v>
       </c>
@@ -15833,27 +18737,39 @@
         <v>248.8416666666667</v>
       </c>
       <c r="C25" s="3">
+        <f t="shared" si="1"/>
+        <v>-116.34338235294109</v>
+      </c>
+      <c r="D25" s="4">
         <f t="shared" si="0"/>
-        <v>-116.34338235294109</v>
-      </c>
-      <c r="D25" s="4">
-        <f>STANDARDIZE(B25,F$1,F$2)</f>
         <v>-1.1863449786176838</v>
       </c>
       <c r="E25" s="5">
         <v>-0.45184879703381298</v>
       </c>
-      <c r="O25" s="6" t="s">
+      <c r="F25" s="5">
+        <f t="shared" si="2"/>
+        <v>-0.95085261414854039</v>
+      </c>
+      <c r="G25" s="5">
+        <f t="shared" si="3"/>
+        <v>1.0775287556750187E-2</v>
+      </c>
+      <c r="H25" s="5">
+        <f t="shared" si="4"/>
+        <v>0.31547614610556618</v>
+      </c>
+      <c r="R25" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="P25" s="7" t="s">
+      <c r="S25" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="Q25" s="7" t="s">
+      <c r="T25" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>1991</v>
       </c>
@@ -15861,27 +18777,39 @@
         <v>242.79999999999998</v>
       </c>
       <c r="C26" s="3">
+        <f t="shared" si="1"/>
+        <v>-122.38504901960781</v>
+      </c>
+      <c r="D26" s="4">
         <f t="shared" si="0"/>
-        <v>-122.38504901960781</v>
-      </c>
-      <c r="D26" s="4">
-        <f>STANDARDIZE(B26,F$1,F$2)</f>
         <v>-1.2479514126711346</v>
       </c>
       <c r="E26" s="5">
         <v>0.40128082574528251</v>
       </c>
-      <c r="O26" s="14" t="s">
+      <c r="F26" s="5">
+        <f t="shared" si="2"/>
+        <v>-0.97824269310471823</v>
+      </c>
+      <c r="G26" s="5">
+        <f t="shared" si="3"/>
+        <v>0.42258857809141764</v>
+      </c>
+      <c r="H26" s="5">
+        <f t="shared" si="4"/>
+        <v>0.52125986203243557</v>
+      </c>
+      <c r="R26" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="P26" s="15">
+      <c r="S26" s="13">
         <v>0</v>
       </c>
-      <c r="Q26" s="12">
+      <c r="T26" s="10">
         <v>0.56509980556847084</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>1990</v>
       </c>
@@ -15889,27 +18817,39 @@
         <v>316.10833333333335</v>
       </c>
       <c r="C27" s="3">
+        <f t="shared" si="1"/>
+        <v>-49.07671568627444</v>
+      </c>
+      <c r="D27" s="4">
         <f t="shared" si="0"/>
-        <v>-49.07671568627444</v>
-      </c>
-      <c r="D27" s="4">
-        <f>STANDARDIZE(B27,F$1,F$2)</f>
         <v>-0.500431688025336</v>
       </c>
       <c r="E27" s="5">
         <v>1.3183337055627835</v>
       </c>
-      <c r="O27" s="16" t="s">
+      <c r="F27" s="5">
+        <f t="shared" si="2"/>
+        <v>-0.56877942382808377</v>
+      </c>
+      <c r="G27" s="5">
+        <f t="shared" si="3"/>
+        <v>0.99175142441240327</v>
+      </c>
+      <c r="H27" s="5">
+        <f t="shared" si="4"/>
+        <v>0.68860338364098439</v>
+      </c>
+      <c r="R27" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="P27" s="13">
+      <c r="S27" s="11">
         <v>0.56509980556847084</v>
       </c>
-      <c r="Q27" s="19">
+      <c r="T27" s="17">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>1989</v>
       </c>
@@ -15917,21 +18857,33 @@
         <v>369.30833333333334</v>
       </c>
       <c r="C28" s="3">
+        <f t="shared" si="1"/>
+        <v>4.1232843137255486</v>
+      </c>
+      <c r="D28" s="4">
         <f t="shared" si="0"/>
-        <v>4.1232843137255486</v>
-      </c>
-      <c r="D28" s="4">
-        <f>STANDARDIZE(B28,F$1,F$2)</f>
         <v>4.2044829212219553E-2</v>
       </c>
       <c r="E28" s="5">
         <v>1.2556397419291438</v>
       </c>
-      <c r="O28" s="18" t="s">
+      <c r="F28" s="5">
+        <f t="shared" si="2"/>
+        <v>9.1924797197565009E-2</v>
+      </c>
+      <c r="G28" s="5">
+        <f t="shared" si="3"/>
+        <v>1.1645282964978174</v>
+      </c>
+      <c r="H28" s="5">
+        <f t="shared" si="4"/>
+        <v>0.77448589427164682</v>
+      </c>
+      <c r="R28" s="16" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>1988</v>
       </c>
@@ -15939,18 +18891,30 @@
         <v>437.18333333333334</v>
       </c>
       <c r="C29" s="3">
+        <f t="shared" si="1"/>
+        <v>71.998284313725549</v>
+      </c>
+      <c r="D29" s="4">
         <f t="shared" si="0"/>
-        <v>71.998284313725549</v>
-      </c>
-      <c r="D29" s="4">
-        <f>STANDARDIZE(B29,F$1,F$2)</f>
         <v>0.73416125040581148</v>
       </c>
       <c r="E29" s="5">
         <v>0.91961144200152467</v>
       </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="F29" s="5">
+        <f t="shared" si="2"/>
+        <v>7.9801783967736586E-2</v>
+      </c>
+      <c r="G29" s="5">
+        <f t="shared" si="3"/>
+        <v>0.71760498001672268</v>
+      </c>
+      <c r="H29" s="5">
+        <f t="shared" si="4"/>
+        <v>0.73680294198614538</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>1987</v>
       </c>
@@ -15958,18 +18922,30 @@
         <v>312.54166666666669</v>
       </c>
       <c r="C30" s="3">
+        <f t="shared" si="1"/>
+        <v>-52.643382352941103</v>
+      </c>
+      <c r="D30" s="4">
         <f t="shared" si="0"/>
-        <v>-52.643382352941103</v>
-      </c>
-      <c r="D30" s="4">
-        <f>STANDARDIZE(B30,F$1,F$2)</f>
         <v>-0.53680072771482124</v>
       </c>
       <c r="E30" s="5">
         <v>-2.2436243880499956E-2</v>
       </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="F30" s="5">
+        <f t="shared" si="2"/>
+        <v>-9.7058250160881585E-2</v>
+      </c>
+      <c r="G30" s="5">
+        <f t="shared" si="3"/>
+        <v>0.37001375414626653</v>
+      </c>
+      <c r="H30" s="5">
+        <f t="shared" si="4"/>
+        <v>0.47940378464697792</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>1986</v>
       </c>
@@ -15977,21 +18953,33 @@
         <v>317.27500000000003</v>
       </c>
       <c r="C31" s="3">
+        <f t="shared" si="1"/>
+        <v>-47.910049019607754</v>
+      </c>
+      <c r="D31" s="4">
         <f t="shared" si="0"/>
-        <v>-47.910049019607754</v>
-      </c>
-      <c r="D31" s="4">
-        <f>STANDARDIZE(B31,F$1,F$2)</f>
         <v>-0.48853527317363499</v>
       </c>
       <c r="E31" s="5">
         <v>0.2128660643177748</v>
       </c>
-      <c r="O31" t="s">
+      <c r="F31" s="5">
+        <f t="shared" si="2"/>
+        <v>-0.54963186087629834</v>
+      </c>
+      <c r="G31" s="5">
+        <f t="shared" si="3"/>
+        <v>7.3922579768073815E-2</v>
+      </c>
+      <c r="H31" s="5">
+        <f t="shared" si="4"/>
+        <v>0.29544373075828723</v>
+      </c>
+      <c r="R31" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>1985</v>
       </c>
@@ -15999,18 +18987,30 @@
         <v>304.03333333333336</v>
       </c>
       <c r="C32" s="3">
+        <f t="shared" si="1"/>
+        <v>-61.151715686274429</v>
+      </c>
+      <c r="D32" s="4">
         <f t="shared" si="0"/>
-        <v>-61.151715686274429</v>
-      </c>
-      <c r="D32" s="4">
-        <f>STANDARDIZE(B32,F$1,F$2)</f>
         <v>-0.62355958174043891</v>
       </c>
       <c r="E32" s="5">
         <v>3.133791886694659E-2</v>
       </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="F32" s="5">
+        <f t="shared" si="2"/>
+        <v>-0.37954145329424321</v>
+      </c>
+      <c r="G32" s="5">
+        <f t="shared" si="3"/>
+        <v>0.1933478185568038</v>
+      </c>
+      <c r="H32" s="5">
+        <f t="shared" si="4"/>
+        <v>5.2189959691108734E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>1984</v>
       </c>
@@ -16018,27 +19018,39 @@
         <v>362.58333333333331</v>
       </c>
       <c r="C33" s="3">
+        <f t="shared" si="1"/>
+        <v>-2.6017156862744741</v>
+      </c>
+      <c r="D33" s="4">
         <f t="shared" si="0"/>
-        <v>-2.6017156862744741</v>
-      </c>
-      <c r="D33" s="4">
-        <f>STANDARDIZE(B33,F$1,F$2)</f>
         <v>-2.6529504968655897E-2</v>
       </c>
       <c r="E33" s="5">
         <v>0.33583947248568996</v>
       </c>
-      <c r="O33" s="6" t="s">
+      <c r="F33" s="5">
+        <f t="shared" si="2"/>
+        <v>-0.92425562951580942</v>
+      </c>
+      <c r="G33" s="5">
+        <f t="shared" si="3"/>
+        <v>2.3506659339422958E-2</v>
+      </c>
+      <c r="H33" s="5">
+        <f t="shared" si="4"/>
+        <v>8.4231070388026824E-2</v>
+      </c>
+      <c r="R33" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="P33" s="7" t="s">
+      <c r="S33" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="Q33" s="7" t="s">
+      <c r="T33" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>1983</v>
       </c>
@@ -16046,27 +19058,39 @@
         <v>157.01666666666668</v>
       </c>
       <c r="C34" s="3">
+        <f t="shared" si="1"/>
+        <v>-208.16838235294111</v>
+      </c>
+      <c r="D34" s="4">
         <f t="shared" si="0"/>
-        <v>-208.16838235294111</v>
-      </c>
-      <c r="D34" s="4">
-        <f>STANDARDIZE(B34,F$1,F$2)</f>
         <v>-2.1226778018383334</v>
       </c>
       <c r="E34" s="5">
         <v>-0.29665741333436768</v>
       </c>
-      <c r="O34" s="14" t="s">
+      <c r="F34" s="5">
+        <f t="shared" si="2"/>
+        <v>-1.1428947396117104</v>
+      </c>
+      <c r="G34" s="5">
+        <f t="shared" si="3"/>
+        <v>5.8983789585137558E-2</v>
+      </c>
+      <c r="H34" s="5">
+        <f>AVERAGE(E32:E35)</f>
+        <v>5.2072321905589816E-2</v>
+      </c>
+      <c r="R34" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="P34" s="15">
+      <c r="S34" s="13">
         <v>1</v>
       </c>
-      <c r="Q34" s="12">
+      <c r="T34" s="10">
         <v>1.0449919725998263E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>1982</v>
       </c>
@@ -16074,27 +19098,39 @@
         <v>239.70833333333334</v>
       </c>
       <c r="C35" s="3">
+        <f t="shared" si="1"/>
+        <v>-125.47671568627445</v>
+      </c>
+      <c r="D35" s="4">
         <f t="shared" si="0"/>
-        <v>-125.47671568627445</v>
-      </c>
-      <c r="D35" s="4">
-        <f>STANDARDIZE(B35,F$1,F$2)</f>
         <v>-1.2794769120281415</v>
       </c>
       <c r="E35" s="5">
         <v>0.1377693096040904</v>
       </c>
-      <c r="O35" s="16" t="s">
+      <c r="F35" s="5">
+        <f>AVERAGE(D34:D35)</f>
+        <v>-1.7010773569332374</v>
+      </c>
+      <c r="G35" s="5">
+        <f>AVERAGE(E34:E35)</f>
+        <v>-7.9444051865138643E-2</v>
+      </c>
+      <c r="H35" s="5">
+        <f>AVERAGE(E33:E35)</f>
+        <v>5.8983789585137558E-2</v>
+      </c>
+      <c r="R35" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="P35" s="13">
+      <c r="S35" s="11">
         <v>1.0449919725998263E-2</v>
       </c>
-      <c r="Q35" s="17">
+      <c r="T35" s="15">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
       <c r="D36" s="4"/>
